--- a/Calculation Module/MoneyKeel-calculation-master-v1.xlsx
+++ b/Calculation Module/MoneyKeel-calculation-master-v1.xlsx
@@ -7,16 +7,17 @@
   </bookViews>
   <sheets>
     <sheet name="0. Read Me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1. Metric Matrix" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="1. Metrics" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2. Engines" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="3. Work list" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2. Field Crosswalk" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="3. By Asset Class" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="4. Gaps &amp; Decisions" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="5. SnapTrade" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="6. Transaction Taxonomy" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="7. Cost Basis" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="8. Snapshot &amp; Honesty" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="4. Architecture" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5. Transaction taxonomy" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="6. Field crosswalk" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="7. By asset class" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="8. Cost basis" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="9. Snapshot &amp; honesty" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="10. Gaps &amp; decisions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="11. SnapTrade" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -26,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -170,8 +171,18 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001B4D8F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001B3A5C"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -266,6 +277,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -399,7 +415,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -529,6 +545,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1096,307 +1121,298 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="68" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>Cost basis - three definitions, one decision table</t>
+          <t>The snapshot store, and what to show when a return would mislead</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Named on the Gaps tab, resolved here. The three are not interchangeable and the weakest is the one MoneyKeel currently holds.</t>
+          <t>Answers to the two specific questions in the brief. Thresholds marked as OUR choice are decisions to review, not facts.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="34" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Question</t>
         </is>
       </c>
       <c r="B4" s="34" t="inlineStr">
         <is>
-          <t>What it includes</t>
+          <t>Answer</t>
         </is>
       </c>
       <c r="C4" s="34" t="inlineStr">
         <is>
-          <t>Who gives you this</t>
-        </is>
-      </c>
-      <c r="D4" s="34" t="inlineStr">
-        <is>
-          <t>Worth for tax reporting</t>
-        </is>
-      </c>
-      <c r="E4" s="34" t="inlineStr">
-        <is>
-          <t>What it does to unrealised gain</t>
-        </is>
-      </c>
-      <c r="F4" s="34" t="inlineStr">
-        <is>
-          <t>What the screen must say when this is all you hold</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+          <t>Why</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
       <c r="A5" s="35" t="inlineStr">
         <is>
-          <t>THE THREE DEFINITIONS</t>
+          <t>THE SNAPSHOT STORE - minimum viable daily record</t>
         </is>
       </c>
       <c r="B5" s="35" t="n"/>
       <c r="C5" s="35" t="n"/>
-      <c r="D5" s="35" t="n"/>
-      <c r="E5" s="35" t="n"/>
-      <c r="F5" s="35" t="n"/>
-    </row>
-    <row r="6" ht="70" customHeight="1">
+    </row>
+    <row r="6" ht="56" customHeight="1">
       <c r="A6" s="36" t="inlineStr">
         <is>
-          <t>Lot-level, fees included</t>
+          <t>What is wrong with one number a day</t>
         </is>
       </c>
       <c r="B6" s="36" t="inlineStr">
         <is>
-          <t>Each batch of shares, its own purchase date and price, with commission and fees added in. Adjusted over time by reinvested income (up) and return of capital (down).</t>
+          <t>One household total per day cannot be split back into accounts or holdings. It cannot give a beginning value for ONE account, cannot weight a holding at the start of a period, and cannot be reconciled against any statement. Everything blocked in column J is blocked by this one shape.</t>
         </is>
       </c>
       <c r="C6" s="36" t="inlineStr">
         <is>
-          <t>FDX taxLots[].costBasis and Plaid Core Exchange taxLots[] where the institution supports lots; SnapTrade tax_lots[] where the institution supports lots. Both of MoneyKeel's live brokers sent NONE.</t>
-        </is>
-      </c>
-      <c r="D6" s="36" t="inlineStr">
-        <is>
-          <t>The only one that can produce a defensible long-versus-short split, because only it holds a real purchase date per batch. Still an estimate: the broker's own 1099-B is what the IRS sees.</t>
-        </is>
-      </c>
-      <c r="E6" s="36" t="inlineStr">
-        <is>
-          <t>Correct, and correct per batch - which is what a person needs when deciding which shares to sell.</t>
-        </is>
-      </c>
-      <c r="F6" s="36" t="inlineStr">
-        <is>
-          <t>Nothing special. Say which lots the figures came from.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="70" customHeight="1">
+          <t>Every metric that needs a beginning value needs it at the level the question is asked - and the questions are asked per account and per holding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
       <c r="A7" s="36" t="inlineStr">
         <is>
-          <t>Holding average, commission included</t>
+          <t>Grain</t>
         </is>
       </c>
       <c r="B7" s="36" t="inlineStr">
         <is>
-          <t>One average cost per share across the whole position, with commission in. No purchase dates.</t>
+          <t>One row per account per holding per date, PLUS one row per account per date for cash and the broker's own stated total. Written after the broker's close, stamped with the broker's date, not the server's.</t>
         </is>
       </c>
       <c r="C7" s="36" t="inlineStr">
         <is>
-          <t>Yodlee costBasis. SnapTrade average_purchase_price (whether fees are inside is per broker - UNKNOWN in general).</t>
-        </is>
-      </c>
-      <c r="D7" s="36" t="inlineStr">
-        <is>
-          <t>Enough for a total gain figure. CANNOT split long from short, because there is no purchase date to judge. Mutual funds are commonly held this way by the broker too, so for funds this often matches what the broker reports.</t>
-        </is>
-      </c>
-      <c r="E7" s="36" t="inlineStr">
-        <is>
-          <t>Correct in total, meaningless per batch.</t>
-        </is>
-      </c>
-      <c r="F7" s="36" t="inlineStr">
-        <is>
-          <t>'This is an average across all your shares - we cannot tell which were bought when, so we cannot split the tax treatment.' Then show no long-versus-short split at all rather than a guessed one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="70" customHeight="1">
+          <t>Per-holding is what makes contribution-to-return and the trend line possible. Per-account cash is what lets you reconcile against the statement. The broker's date is what makes 'the same day' mean the same day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
       <c r="A8" s="36" t="inlineStr">
         <is>
-          <t>Price x units, fees excluded</t>
+          <t>Fields - per holding</t>
         </is>
       </c>
       <c r="B8" s="36" t="inlineStr">
         <is>
-          <t>Units multiplied by a purchase price. No commission, no fees, no adjustments.</t>
+          <t>date; account id; security key (your internal one) plus the raw identifiers as received; units; price; price as-of; market value; cost basis; cost basis definition tag; accrued interest where the source gives it; a flag for 'priced' vs 'could not price'.</t>
         </is>
       </c>
       <c r="C8" s="36" t="inlineStr">
         <is>
-          <t>What you get when you derive basis from FDX purchasedPrice x units - FDX carries NO fee field on a holding. This is MoneyKeel's current position: one synthetic lot built from an average price.</t>
-        </is>
-      </c>
-      <c r="D8" s="36" t="inlineStr">
-        <is>
-          <t>Weakest. It understates cost, so it OVERSTATES gain and overstates the tax owed. Never present it as a tax figure.</t>
-        </is>
-      </c>
-      <c r="E8" s="36" t="inlineStr">
-        <is>
-          <t>Overstates the gain by the fees paid, and by every reinvested distribution not added back.</t>
-        </is>
-      </c>
-      <c r="F8" s="36" t="inlineStr">
-        <is>
-          <t>'Estimated from the average price we were given. It does not include trading costs, so your real gain is likely smaller than this.' This is MoneyKeel's live state today and the sentence is missing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="35" t="inlineStr">
-        <is>
-          <t>THE DECISION</t>
-        </is>
-      </c>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n"/>
-      <c r="F9" s="35" t="n"/>
-    </row>
-    <row r="10" ht="56" customHeight="1">
+          <t>Units and price separately, never just value: a value alone cannot tell you later whether a change was a price move or a share move, which is the distinction the whole Performance screen rests on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="36" t="inlineStr">
+        <is>
+          <t>Fields - per account</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="inlineStr">
+        <is>
+          <t>date; uninvested cash; the broker's own stated account total; the sum of the day's flows by canonical bucket (contributions, withdrawals, income, fees, tax); count of unmapped events that day; last successful sync time.</t>
+        </is>
+      </c>
+      <c r="C9" s="36" t="inlineStr">
+        <is>
+          <t>The broker's stated total is the only external check you get for free. Storing the day's flows beside the value is what makes Modified Dietz a lookup rather than a re-derivation of the entire ledger every time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
       <c r="A10" s="36" t="inlineStr">
         <is>
-          <t>Store the tag, not just the number</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="B10" s="36" t="inlineStr">
         <is>
-          <t>Every basis figure carries which of the three it is, and where it came from. Two figures with different tags are never added, compared, or shown in the same total without saying so.</t>
+          <t>Daily rows for 24 months. Month-end rows FOREVER, never pruned. Every transaction forever - they are small, and they are the only thing that can rebuild a snapshot you deleted.</t>
         </is>
       </c>
       <c r="C10" s="36" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="56" customHeight="1">
+          <t>400 days makes '5 years' and 'since I started' permanently unanswerable for a 55-70 audience whose whole question is the long run. Month-end forever costs almost nothing: roughly 12 rows per holding per year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
       <c r="A11" s="36" t="inlineStr">
         <is>
-          <t>Rank, and fall back downward only</t>
+          <t>Size, roughly</t>
         </is>
       </c>
       <c r="B11" s="36" t="inlineStr">
         <is>
-          <t>Lot-with-fees beats holding-average beats price-x-units. Take the best available per holding, per broker - not one choice for the whole app - and never upgrade a weaker figure by inventing the missing part.</t>
+          <t>Three accounts, 20 holdings each, daily for two years is on the order of 45,000 rows per person - kilobytes, not megabytes. Month-end forever adds about 700 rows a year.</t>
         </is>
       </c>
       <c r="C11" s="36" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="98" customHeight="1">
+          <t>The reason not to store this was never cost. Say so plainly, because 'too much data' will be the objection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
       <c r="A12" s="36" t="inlineStr">
         <is>
-          <t>Basis is not static</t>
+          <t>Corrections</t>
         </is>
       </c>
       <c r="B12" s="36" t="inlineStr">
         <is>
-          <t>Whatever the source, the app must adjust it as events arrive: reinvested income increases it, return of capital reduces it, a split leaves the total unchanged but changes it per share, an in-kind transfer must carry it across. A basis copied once from a broker and never adjusted drifts furthest for the long-held fund positions this audience has most of.</t>
+          <t>A snapshot is immutable once written. When a broker restates a past day, write a NEW row for that date with a version, and keep the old one. Show the person the latest, keep the earlier for the day a number changes and someone asks why.</t>
         </is>
       </c>
       <c r="C12" s="36" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="84" customHeight="1">
+          <t>Late corrections are normal - trades settle, prices get restated, files get re-imported. Overwriting in place means history silently changes and no figure can ever be reproduced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="56" customHeight="1">
       <c r="A13" s="36" t="inlineStr">
         <is>
-          <t>What the person sees</t>
+          <t>First connection</t>
         </is>
       </c>
       <c r="B13" s="36" t="inlineStr">
         <is>
-          <t>One line under every gain figure naming the weakest ingredient in it. A retiree does not need the word 'provenance'; they need to know whether the number is good enough to act on. 'Good enough to see how you're doing, not good enough for your tax return' is the honest version, and it is true for all three definitions.</t>
+          <t>Backfill from the transaction history you can get - and mark every reconstructed day as reconstructed, not measured. SnapTrade's historical account value endpoint can bootstrap this, but it is experimental, capped and ESTIMATED: use it to draw a line, never as the beginning value in a return calculation.</t>
         </is>
       </c>
       <c r="C13" s="36" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>A reconstructed history is much better than none and much worse than a measurement. The distinction has to survive into the data, or it will not survive onto the screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>SHORT WINDOWS - what to show when a number is computable but not meaningful</t>
+        </is>
+      </c>
+      <c r="B14" s="35" t="n"/>
+      <c r="C14" s="35" t="n"/>
+    </row>
+    <row r="15" ht="70" customHeight="1">
+      <c r="A15" s="36" t="inlineStr">
+        <is>
+          <t>The test, stated once</t>
+        </is>
+      </c>
+      <c r="B15" s="36" t="inlineStr">
+        <is>
+          <t>Refuse the RATE - not the whole screen - when any of these is true: the window is under about 30 days; net flows exceed roughly 10% of the beginning value; the holding was not held for the whole window; the beginning value is missing, reconstructed, or near zero; or any unmapped event touched the account in the window. These thresholds are OUR choice and belong in one named place, not scattered through the code.</t>
+        </is>
+      </c>
+      <c r="C15" s="36" t="inlineStr">
+        <is>
+          <t>Each condition makes the percentage answer a different question from the one the person asked. The first four are arithmetic; the last is honesty about the ledger underneath.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="A16" s="36" t="inlineStr">
+        <is>
+          <t>What to show instead - always the dollars</t>
+        </is>
+      </c>
+      <c r="B16" s="36" t="inlineStr">
+        <is>
+          <t>Show the money: what it was worth, what went in, what came out, what it is worth now. Dollars are always well-defined even when a rate is not, and for this audience they are the more useful number anyway. 'Your account went from $378,022 to $391,540. You added $10,000. The rest, $3,518, is what your investments did.'</t>
+        </is>
+      </c>
+      <c r="C16" s="36" t="inlineStr">
+        <is>
+          <t>Answers the real question - am I ahead - without ever dividing by a beginning value that may be missing or tiny. This is also the sentence that makes the residual visible, which is what row 12 of the metric matrix demands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="36" t="inlineStr">
+        <is>
+          <t>Never show 'nothing'</t>
+        </is>
+      </c>
+      <c r="B17" s="36" t="inlineStr">
+        <is>
+          <t>A blank is its own confusion. Show the dollars, then one plain line saying why there is no percentage: 'A percentage over ten days would be mostly noise' or 'You added money during this period, so a single percentage would be misleading'. Name the reason, not a generic apology.</t>
+        </is>
+      </c>
+      <c r="C17" s="36" t="inlineStr">
+        <is>
+          <t>'Not available' reads as a broken app. 'A percentage here would mislead you' reads as an app that is being careful, which is the reputation worth having with people who have one pot of money and no second chance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="36" t="inlineStr">
+        <is>
+          <t>A holding bought mid-period</t>
+        </is>
+      </c>
+      <c r="B18" s="36" t="inlineStr">
+        <is>
+          <t>Show its own return since purchase, labelled with the purchase date, and keep it out of any period figure that claims to cover the whole window - including out of the winners-and-detractors list unless weighted by the share of the period it was held.</t>
+        </is>
+      </c>
+      <c r="C18" s="36" t="inlineStr">
+        <is>
+          <t>This is exactly the defect in rows 30, 59, 60 and 62. Fixing it in the UI rule and the calculation together is what stops it coming back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="36" t="inlineStr">
+        <is>
+          <t>Never annualise a short window</t>
+        </is>
+      </c>
+      <c r="B19" s="36" t="inlineStr">
+        <is>
+          <t>Under a year, show the period figure only, labelled with its dates. No 'equivalent annual rate', not even in small print.</t>
+        </is>
+      </c>
+      <c r="C19" s="36" t="inlineStr">
+        <is>
+          <t>Ten days of ordinary movement annualises into a number that looks like a crisis or a windfall. The metric matrix says this twice; it belongs in the UI rules too.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="36" t="inlineStr">
+        <is>
+          <t>Say what the number is measured FROM</t>
+        </is>
+      </c>
+      <c r="B20" s="36" t="inlineStr">
+        <is>
+          <t>Every change figure carries its start date in the label. If the true start is the day the app was installed, the label says that.</t>
+        </is>
+      </c>
+      <c r="C20" s="36" t="inlineStr">
+        <is>
+          <t>A figure measured from install day, presented as 'this year', is wrong in a way the person cannot detect and would care about if they could.</t>
         </is>
       </c>
     </row>
@@ -1411,298 +1427,604 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="82" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Gaps, workarounds, and the decisions you must make explicitly</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Gap / decision</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Why it matters for your 10-day view</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>No historical valuation in any consumer standard</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Beginning value at T-10 simply is not retrievable. Every metric on Sheet 1 that needs BMV depends on state you own.</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Snapshot holdings and cash daily on connection and persist them. Treat your snapshot store as the system of record for performance; treat the API as the system of record for current position.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>No performance field anywhere on the consumer rails</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>You will show a return number the brokerage's own app shows differently.</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Pick one method (Modified Dietz for short windows, chain-linked TWR once you have a daily series), label it in the UI, and keep an IRR alongside for the 'what did I earn' question.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Transaction taxonomy is the real integration cost</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Whether a $5,000 movement is a contribution, a dividend reinvestment, or an internal transfer changes your return, not just a label.</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Build a canonical transaction taxonomy with four axes: direction (in/out), externality (external flow vs internal), economic nature (principal vs income vs fee vs tax), and security-affecting (yes/no). Map every provider enum into it, and keep the raw provider value on the record forever.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Three incompatible cost-basis definitions</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Unrealized gain differs across providers for the same position.</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Store cost basis with a provenance tag (lot-with-fees / average-with-commission / derived-price-x-units) and never mix tags in one rollup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Bond and fixed-income data is thin in FDX</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>No coupon, no maturity, no accrual on the holding - so no yield, no income projection.</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Plan for a security master (or Yodlee/OFX where available) as a required input, not an enhancement. Enrich by ISIN/CUSIP; fall back to a name match only with a confidence flag.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Security identity is not stable</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>FDX allows holdingName as the sole identifier; a spacing change forks a position's history. Plaid's security_id can change on a corporate action.</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Resolve to your own internal security key with a documented precedence (ISIN &gt; CUSIP &gt; SEDOL &gt; ticker+exchange &gt; normalized name) and persist the alias chain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Asset-type enums do not map cleanly</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>FDX's 8 holding types vs Yodlee's ~38 security types. ETFs, commodities, and equity comp have no FDX home.</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Model your own class taxonomy at the granularity of your product, map upward from the widest source, and store the source enum verbatim for audit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>As-of timestamps are unnormalized and often stale</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>A 10-day return computed against a mispriced endpoint is unfalsifiable and wrong.</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Reject or flag any valuation older than your tolerance; do not silently substitute the last known price. FDX does not normalize timezone - normalize on ingest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Corporate actions are inconsistently transmitted</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Splits, spinoffs, and mergers appear as typed transactions in OFX, and sometimes as nothing at all elsewhere.</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Detect unexplained quantity changes (quantity delta with no matching transaction) and quarantine rather than booking a phantom gain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Fees are partly invisible</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Advisory and wrap fees are sometimes netted into NAV or unit price before you ever see them.</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Report gross and net where you can separate them, and disclose when you cannot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Holding-level currency can differ from account currency in FDX.</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Store amount + currency as one type. Never sum bare numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Crypto needs 8-18 decimals; a float pipeline loses balances silently.</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Decimal end to end, including your database columns and your JSON serialization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Lookback limits</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Transaction history is commonly 12-24 months, and 'startTime' behavior varies by provider.</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Backfill fully at first connection, persist everything, and never re-derive history from a live call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>1033 landscape</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>The CFPB Personal Financial Data Rights rule pushed FDX toward being the de facto US standard, so FDX's omissions become industry-wide omissions.</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Do not wait for the standard to add performance fields. Assume derivation is permanently your job, and design the snapshot store as core infrastructure rather than a cache.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
-    <col width="68" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="2" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>The snapshot store, and what to show when a return would mislead</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>Answers to the two specific questions in the brief. Thresholds marked as OUR choice are decisions to review, not facts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="34" t="inlineStr">
-        <is>
-          <t>Question</t>
-        </is>
-      </c>
-      <c r="B4" s="34" t="inlineStr">
-        <is>
-          <t>Answer</t>
-        </is>
-      </c>
-      <c r="C4" s="34" t="inlineStr">
-        <is>
-          <t>Why</t>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>SnapTrade - how it compares to the FDX-family rails</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Brokerage-direct, trading-first, and the only source examined that natively names contributions, withdrawals, and rate of return - though those endpoints are legacy or experimental.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>What SnapTrade does</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Implication</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="35" t="inlineStr">
-        <is>
-          <t>THE SNAPSHOT STORE - minimum viable daily record</t>
-        </is>
-      </c>
-      <c r="B5" s="35" t="n"/>
-      <c r="C5" s="35" t="n"/>
-    </row>
-    <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="36" t="inlineStr">
-        <is>
-          <t>What is wrong with one number a day</t>
-        </is>
-      </c>
-      <c r="B6" s="36" t="inlineStr">
-        <is>
-          <t>One household total per day cannot be split back into accounts or holdings. It cannot give a beginning value for ONE account, cannot weight a holding at the start of a period, and cannot be reconciled against any statement. Everything blocked in column J is blocked by this one shape.</t>
-        </is>
-      </c>
-      <c r="C6" s="36" t="inlineStr">
-        <is>
-          <t>Every metric that needs a beginning value needs it at the level the question is asked - and the questions are asked per account and per holding.</t>
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>WHERE SNAPTRADE IS STRUCTURALLY DIFFERENT</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n"/>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Not an FDX implementation</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>SnapTrade is brokerage-direct and trading-first (Robinhood, Schwab, Fidelity, IBKR, crypto venues), not a 1033/FDX data-sharing rail. Its schema owes nothing to FDX and everything to broker order-management models.</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Do not expect FDX field names or FDX certification semantics. Map it as its own source, not as an FDX variant.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="36" t="inlineStr">
-        <is>
-          <t>Grain</t>
-        </is>
-      </c>
-      <c r="B7" s="36" t="inlineStr">
-        <is>
-          <t>One row per account per holding per date, PLUS one row per account per date for cash and the broker's own stated total. Written after the broker's close, stamped with the broker's date, not the server's.</t>
-        </is>
-      </c>
-      <c r="C7" s="36" t="inlineStr">
-        <is>
-          <t>Per-holding is what makes contribution-to-return and the trend line possible. Per-account cash is what lets you reconcile against the statement. The broker's date is what makes 'the same day' mean the same day.</t>
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>It ships P&amp;L</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>open_pnl on each position - profit or loss since the position was opened. FDX, Plaid Core Exchange, and MX ship no P&amp;L field at all.</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Useful for display parity with the broker's own app. Do not mix it into your own computed gain - the broker's basis convention is not yours. SnapTrade's own docs suggest deriving from average_purchase_price.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="36" t="inlineStr">
-        <is>
-          <t>Fields - per holding</t>
-        </is>
-      </c>
-      <c r="B8" s="36" t="inlineStr">
-        <is>
-          <t>date; account id; security key (your internal one) plus the raw identifiers as received; units; price; price as-of; market value; cost basis; cost basis definition tag; accrued interest where the source gives it; a flag for 'priced' vs 'could not price'.</t>
-        </is>
-      </c>
-      <c r="C8" s="36" t="inlineStr">
-        <is>
-          <t>Units and price separately, never just value: a value alone cannot tell you later whether a change was a price move or a share move, which is the distinction the whole Performance screen rests on.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="36" t="inlineStr">
-        <is>
-          <t>Fields - per account</t>
-        </is>
-      </c>
-      <c r="B9" s="36" t="inlineStr">
-        <is>
-          <t>date; uninvested cash; the broker's own stated account total; the sum of the day's flows by canonical bucket (contributions, withdrawals, income, fees, tax); count of unmapped events that day; last successful sync time.</t>
-        </is>
-      </c>
-      <c r="C9" s="36" t="inlineStr">
-        <is>
-          <t>The broker's stated total is the only external check you get for free. Storing the day's flows beside the value is what makes Modified Dietz a lookup rather than a re-derivation of the entire ledger every time.</t>
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>It has a historical value endpoint</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>getAccountBalanceHistory returns estimated historical total account value (positions + cash). This is the only consumer-rail approximation of your T-10 beginning value that I found.</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Experimental, disabled by default, capped lookback, and estimated. Use it to bootstrap a new connection's history; do not make it the basis of a headline return. Keep your own daily snapshot as the system of record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>It once had a performance API</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>A PerformanceCustom schema exists in the SDK spec: totalEquityTimeframe, contributions, contributionTimeframe, contributionTimeframeCumulative, withdrawalTimeframe, contributionStreak, dividends, plus rate-of-return timeframes ALL / 1Y / YTD / 1M / 1W / 1D.</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>This is exactly your requested vocabulary - beginning value series, contributions, withdrawals, ROI over a period - and no other rail names these concepts natively. But it is absent from the current documentation index, so treat it as legacy or experimental and confirm availability with SnapTrade before you design a product around it.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="36" t="inlineStr">
-        <is>
-          <t>Retention</t>
-        </is>
-      </c>
-      <c r="B10" s="36" t="inlineStr">
-        <is>
-          <t>Daily rows for 24 months. Month-end rows FOREVER, never pruned. Every transaction forever - they are small, and they are the only thing that can rebuild a snapshot you deleted.</t>
-        </is>
-      </c>
-      <c r="C10" s="36" t="inlineStr">
-        <is>
-          <t>400 days makes '5 years' and 'since I started' permanently unanswerable for a 55-70 audience whose whole question is the long run. Month-end forever costs almost nothing: roughly 12 rows per holding per year.</t>
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Asset-class coverage is the widest</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>instrument.kind discriminates stock, etf, mutualfund, cef, adr, crypto, future, option, cfd, other - with option and future contract metadata (strike, expiration, multiplier) and CFD wrappers.</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Your ETF, crypto, commodity/futures, and option requirements are all first-class here, where FDX collapses them into STOCK or OTHER. This is the strongest argument for SnapTrade as your investment source.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="36" t="inlineStr">
-        <is>
-          <t>Size, roughly</t>
-        </is>
-      </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Three accounts, 20 holdings each, daily for two years is on the order of 45,000 rows per person - kilobytes, not megabytes. Month-end forever adds about 700 rows a year.</t>
-        </is>
-      </c>
-      <c r="C11" s="36" t="inlineStr">
-        <is>
-          <t>The reason not to store this was never cost. Say so plainly, because 'too much data' will be the objection.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="36" t="inlineStr">
-        <is>
-          <t>Corrections</t>
-        </is>
-      </c>
-      <c r="B12" s="36" t="inlineStr">
-        <is>
-          <t>A snapshot is immutable once written. When a broker restates a past day, write a NEW row for that date with a version, and keep the old one. Show the person the latest, keep the earlier for the day a number changes and someone asks why.</t>
-        </is>
-      </c>
-      <c r="C12" s="36" t="inlineStr">
-        <is>
-          <t>Late corrections are normal - trades settle, prices get restated, files get re-imported. Overwriting in place means history silently changes and no figure can ever be reproduced.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="56" customHeight="1">
-      <c r="A13" s="36" t="inlineStr">
-        <is>
-          <t>First connection</t>
-        </is>
-      </c>
-      <c r="B13" s="36" t="inlineStr">
-        <is>
-          <t>Backfill from the transaction history you can get - and mark every reconstructed day as reconstructed, not measured. SnapTrade's historical account value endpoint can bootstrap this, but it is experimental, capped and ESTIMATED: use it to draw a line, never as the beginning value in a return calculation.</t>
-        </is>
-      </c>
-      <c r="C13" s="36" t="inlineStr">
-        <is>
-          <t>A reconstructed history is much better than none and much worse than a measurement. The distinction has to survive into the data, or it will not survive onto the screen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="35" t="inlineStr">
-        <is>
-          <t>SHORT WINDOWS - what to show when a number is computable but not meaningful</t>
-        </is>
-      </c>
-      <c r="B14" s="35" t="n"/>
-      <c r="C14" s="35" t="n"/>
-    </row>
-    <row r="15" ht="70" customHeight="1">
-      <c r="A15" s="36" t="inlineStr">
-        <is>
-          <t>The test, stated once</t>
-        </is>
-      </c>
-      <c r="B15" s="36" t="inlineStr">
-        <is>
-          <t>Refuse the RATE - not the whole screen - when any of these is true: the window is under about 30 days; net flows exceed roughly 10% of the beginning value; the holding was not held for the whole window; the beginning value is missing, reconstructed, or near zero; or any unmapped event touched the account in the window. These thresholds are OUR choice and belong in one named place, not scattered through the code.</t>
-        </is>
-      </c>
-      <c r="C15" s="36" t="inlineStr">
-        <is>
-          <t>Each condition makes the percentage answer a different question from the one the person asked. The first four are arithmetic; the last is honesty about the ledger underneath.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="56" customHeight="1">
-      <c r="A16" s="36" t="inlineStr">
-        <is>
-          <t>What to show instead - always the dollars</t>
-        </is>
-      </c>
-      <c r="B16" s="36" t="inlineStr">
-        <is>
-          <t>Show the money: what it was worth, what went in, what came out, what it is worth now. Dollars are always well-defined even when a rate is not, and for this audience they are the more useful number anyway. 'Your account went from $378,022 to $391,540. You added $10,000. The rest, $3,518, is what your investments did.'</t>
-        </is>
-      </c>
-      <c r="C16" s="36" t="inlineStr">
-        <is>
-          <t>Answers the real question - am I ahead - without ever dividing by a beginning value that may be missing or tiny. This is also the sentence that makes the residual visible, which is what row 12 of the metric matrix demands.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="56" customHeight="1">
-      <c r="A17" s="36" t="inlineStr">
-        <is>
-          <t>Never show 'nothing'</t>
-        </is>
-      </c>
-      <c r="B17" s="36" t="inlineStr">
-        <is>
-          <t>A blank is its own confusion. Show the dollars, then one plain line saying why there is no percentage: 'A percentage over ten days would be mostly noise' or 'You added money during this period, so a single percentage would be misleading'. Name the reason, not a generic apology.</t>
-        </is>
-      </c>
-      <c r="C17" s="36" t="inlineStr">
-        <is>
-          <t>'Not available' reads as a broken app. 'A percentage here would mislead you' reads as an app that is being careful, which is the reputation worth having with people who have one pot of money and no second chance.</t>
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Transaction history is deeper</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Activities often cover the full account history since inception, and are explicitly typed for buys, sells, dividends, contributions, withdrawals.</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>This is what makes Modified Dietz and XIRR feasible over long windows. Plaid/Yodlee lookback is typically 12-24 months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>WHERE IT IS WEAKER THAN THE FDX RAILS</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>No CUSIP or ISIN</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Identity is a SnapTrade UUID plus symbol, exchange MIC, and FIGI (figi_code, figi_share_class).</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>If your security master keys on CUSIP/ISIN, you need a FIGI-to-CUSIP bridge. FIGI is free and unlicensed, which is arguably an advantage - but it is a different join key.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Fixed income is thin to absent</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>No face value, no coupon, no maturity, no accrued interest on positions.</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Worse than Yodlee and OFX for bonds and CDs. If bonds matter, SnapTrade is not your fixed-income source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>No market value field</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Positions carry units and price, not a value. Options and futures carry a multiplier.</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Derive value yourself and apply the multiplier. Forgetting it produces the classic 100x option error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>No asset classification</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>No sector, asset class, or style taxonomy (Yodlee ships all three).</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Buy or build classification for allocation and drift views.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Price freshness is plan-dependent</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Real-time only on the real-time plan; otherwise cached daily with a per-brokerage 'Cache Expiry Time'. Manual refresh available.</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Do not compute a same-day return on daily-cached prices. Their own docs recommend a third-party market data provider for pricing.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="36" t="inlineStr">
-        <is>
-          <t>A holding bought mid-period</t>
-        </is>
-      </c>
-      <c r="B18" s="36" t="inlineStr">
-        <is>
-          <t>Show its own return since purchase, labelled with the purchase date, and keep it out of any period figure that claims to cover the whole window - including out of the winners-and-detractors list unless weighted by the share of the period it was held.</t>
-        </is>
-      </c>
-      <c r="C18" s="36" t="inlineStr">
-        <is>
-          <t>This is exactly the defect in rows 30, 59, 60 and 62. Fixing it in the UI rule and the calculation together is what stops it coming back.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="36" t="inlineStr">
-        <is>
-          <t>Never annualise a short window</t>
-        </is>
-      </c>
-      <c r="B19" s="36" t="inlineStr">
-        <is>
-          <t>Under a year, show the period figure only, labelled with its dates. No 'equivalent annual rate', not even in small print.</t>
-        </is>
-      </c>
-      <c r="C19" s="36" t="inlineStr">
-        <is>
-          <t>Ten days of ordinary movement annualises into a number that looks like a crisis or a windfall. The metric matrix says this twice; it belongs in the UI rules too.</t>
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Type fallback to raw broker strings</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>When an activity type does not fit SnapTrade's common types, it passes through the brokerage's own label verbatim.</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Your canonical taxonomy needs an explicit unmapped bucket plus alerting, not a silent default. Their guidance - lean on amount, units, price, and sign convention rather than the type string - is the right instinct and worth adopting across all your sources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Coverage is brokerage-by-brokerage</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Tax lots, real-time data, and trading are each enabled per institution.</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Feature availability is a per-connection attribute in your data model, not a global flag.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="36" t="inlineStr">
-        <is>
-          <t>Say what the number is measured FROM</t>
-        </is>
-      </c>
-      <c r="B20" s="36" t="inlineStr">
-        <is>
-          <t>Every change figure carries its start date in the label. If the true start is the day the app was installed, the label says that.</t>
-        </is>
-      </c>
-      <c r="C20" s="36" t="inlineStr">
-        <is>
-          <t>A figure measured from install day, presented as 'this year', is wrong in a way the person cannot detect and would care about if they could.</t>
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>HOW TO POSITION IT IN YOUR STACK</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+    </row>
+    <row r="21" ht="56" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Recommended split</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>SnapTrade for brokerage and crypto depth (positions, full activity history, options/futures, P&amp;L, trading). An FDX rail (Plaid Core Exchange / Akoya / MX) for bank, card, loan, and 1033-covered breadth. Yodlee or a security master for fixed income, accrual, and classification.</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Your canonical model absorbs all three. Keep provider, raw type string, and raw identifiers on every record so any normalization decision stays reversible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>What does not change</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Even with SnapTrade, contributions, withdrawals, and return over your 10-day window are yours to derive from activities plus your own snapshot series - unless the performance endpoints prove to be live and supported.</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>The daily snapshot store remains core infrastructure. SnapTrade shortens the backfill; it does not remove the requirement.</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5532,7 @@
       </c>
       <c r="S6" s="45" t="inlineStr">
         <is>
-          <t>src/services/sync/ingest.ts:173</t>
+          <t>src/services/sync/ingest.ts:185</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5620,7 @@
       </c>
       <c r="S7" s="45" t="inlineStr">
         <is>
-          <t>src/services/sync/ingest.ts:29</t>
+          <t>src/services/sync/ingest.ts:34</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9868,7 @@
       </c>
       <c r="S59" s="45" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:226</t>
+          <t>src/domain/performance/index.ts:229</t>
         </is>
       </c>
     </row>
@@ -9628,7 +9950,7 @@
       </c>
       <c r="S60" s="45" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:215</t>
+          <t>src/domain/performance/index.ts:218</t>
         </is>
       </c>
     </row>
@@ -9706,7 +10028,7 @@
       </c>
       <c r="S61" s="45" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:149</t>
+          <t>src/domain/performance/index.ts:152</t>
         </is>
       </c>
     </row>
@@ -10056,7 +10378,7 @@
       </c>
       <c r="S65" s="45" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:128</t>
+          <t>src/domain/performance/index.ts:131</t>
         </is>
       </c>
     </row>
@@ -10453,7 +10775,7 @@
       </c>
       <c r="S70" s="45" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:275</t>
+          <t>src/domain/performance/index.ts:278</t>
         </is>
       </c>
     </row>
@@ -10535,7 +10857,7 @@
       </c>
       <c r="S71" s="45" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:265</t>
+          <t>src/domain/performance/index.ts:268</t>
         </is>
       </c>
     </row>
@@ -10779,7 +11101,7 @@
       </c>
       <c r="S74" s="45" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:205</t>
+          <t>src/domain/performance/index.ts:208</t>
         </is>
       </c>
     </row>
@@ -11990,7 +12312,7 @@
       </c>
       <c r="S89" s="45" t="inlineStr">
         <is>
-          <t>src/services/sync/ingest.ts:31</t>
+          <t>src/services/sync/ingest.ts:36</t>
         </is>
       </c>
     </row>
@@ -14095,7 +14417,7 @@
       </c>
       <c r="S114" s="45" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:119</t>
+          <t>src/domain/performance/index.ts:122</t>
         </is>
       </c>
     </row>
@@ -14186,7 +14508,7 @@
       </c>
       <c r="S115" s="45" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:239</t>
+          <t>src/domain/performance/index.ts:242</t>
         </is>
       </c>
     </row>
@@ -17445,7 +17767,7 @@
       </c>
       <c r="S154" s="45" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:173</t>
+          <t>src/domain/performance/index.ts:176</t>
         </is>
       </c>
     </row>
@@ -17938,7 +18260,7 @@
       </c>
       <c r="S160" s="45" t="inlineStr">
         <is>
-          <t>src/domain/retirement/willItLast.ts:115</t>
+          <t>src/domain/retirement/willItLast.ts:121</t>
         </is>
       </c>
     </row>
@@ -18627,2825 +18949,709 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001B4D8F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Field-name crosswalk by data element</t>
+    <row r="1" ht="52" customHeight="1">
+      <c r="A1" s="51" t="inlineStr">
+        <is>
+          <t>ARCHITECTURE — the whole app as modules and layers, GENERATED from the code and from tab 2 of this file. Read the layers bottom to top: nothing arrives before the thing it is built from. Every count is read off disk, never typed, so this tab cannot quietly disagree with what ships. Rebuild: node "Calculation Module code/scripts/architecture-map.mjs" then this script.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>'NOT PRESENT' means the standard does not transmit it at all. 'VERIFY' means the name comes from documentation summaries, not a field-level read of the licensed spec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Data element</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>FDX v6.x (canonical)</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Plaid Core Exchange (provider side, FDX subset)</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Plaid Investments (recipient side)</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Yodlee v1.1</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>OFX 2.x</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>MX Platform</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>ISO 20022 / SWIFT MT</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>SnapTrade (brokerage-direct)</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>Divergence risk</t>
+      <c r="A2" s="43" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="B2" s="43" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="C2" s="43" t="inlineStr">
+        <is>
+          <t>What it owns</t>
+        </is>
+      </c>
+      <c r="D2" s="43" t="inlineStr">
+        <is>
+          <t>Source files</t>
+        </is>
+      </c>
+      <c r="E2" s="43" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="F2" s="43" t="inlineStr">
+        <is>
+          <t>Engines documented</t>
+        </is>
+      </c>
+      <c r="G2" s="43" t="inlineStr">
+        <is>
+          <t>Needs a fix</t>
+        </is>
+      </c>
+      <c r="H2" s="43" t="inlineStr">
+        <is>
+          <t>Your call</t>
+        </is>
+      </c>
+      <c r="I2" s="43" t="inlineStr">
+        <is>
+          <t>Depends on</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="52" t="inlineStr">
+        <is>
+          <t>1 · Foundation  —  Depends on nothing above it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="44" t="inlineStr">
+        <is>
+          <t>1 · Foundation</t>
+        </is>
+      </c>
+      <c r="B4" s="44" t="inlineStr">
+        <is>
+          <t>foundation</t>
+        </is>
+      </c>
+      <c r="C4" s="44" t="inlineStr">
+        <is>
+          <t>Money formatting, ids, the store, the theme, Firebase, and the market and economic feeds.</t>
+        </is>
+      </c>
+      <c r="D4" s="45" t="n">
+        <v>14</v>
+      </c>
+      <c r="E4" s="45" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I4" s="45" t="inlineStr">
+        <is>
+          <t>net-worth(3) performance(2) cash-flow(2) shared-ui(1)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>ACCOUNT LEVEL</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n"/>
-      <c r="C5" s="9" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="9" t="n"/>
-      <c r="F5" s="9" t="n"/>
-      <c r="G5" s="9" t="n"/>
-      <c r="H5" s="9" t="n"/>
-      <c r="I5" s="8" t="n"/>
-      <c r="J5" s="9" t="n"/>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Account container</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>investmentAccount</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>investmentAccount</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>accounts[] (type=investment)</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>account (container=investment)</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>INVSTMTRS / INVACCTFROM</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>account (type INVESTMENT)</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>semt.002 AcctSubLvl / MT535 :97a::SAFE</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>GET /accounts -&gt; account object (id UUID, institution_name, balance.total)</t>
-        </is>
-      </c>
-      <c r="J6" s="10" t="inlineStr">
-        <is>
-          <t>FDX nests by account-type key; Yodlee uses a flat 'container' discriminator.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Total account value</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>currentValue</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>currentValue</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>balances.current</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>balance / currentBalance</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>INVBAL + position values</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>balance</t>
-        </is>
-      </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>semt.002 TtlHldgsVal</t>
-        </is>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>account.balance.total.amount + .currency (VERIFY)</t>
-        </is>
-      </c>
-      <c r="J7" s="10" t="inlineStr">
-        <is>
-          <t>FDX splits total investments (currentValue) from cash (availableCashBalance); Yodlee 'balance' semantics vary by provider. Do not assume additivity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Cash / sweep balance</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>availableCashBalance</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>availableCashBalance</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>balances.available</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>cash / availableCash</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>INVBAL AVAILCASH, BUYPOWER</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>available_balance</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>GET /accounts/{id}/balances -&gt; cash, buying_power, per currency</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>'Available cash' at a broker can include margin buying power. Treat buying power as a distinct concept.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Valuation as-of timestamp</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>balanceAsOf</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>balanceAsOf</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>close_price_as_of / update_datetime</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>lastUpdated</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>DTASOF</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>balance_updated_at (VERIFY)</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>semt.002 StmtGnlDtls/StmtDtTm</t>
-        </is>
-      </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>sync_status.holdings.last_successful_sync (VERIFY); per-brokerage 'Cache Expiry Time'; real-time only on the real-time plan</t>
-        </is>
-      </c>
-      <c r="J9" s="10" t="inlineStr">
-        <is>
-          <t>The single most abused field. FDX does not normalize timezone; a local time labelled Z is read as UTC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="56" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Beginning-of-period value</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRESENT</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRESENT</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRESENT</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRESENT</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRESENT</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRESENT</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>semt.003 previous statement / MT535 prior report</t>
-        </is>
-      </c>
-      <c r="I10" s="11" t="inlineStr">
-        <is>
-          <t>getAccountBalanceHistory - historical total account value (positions + cash). EXPERIMENTAL, disabled by default, capped lookback.</t>
-        </is>
-      </c>
-      <c r="J10" s="10" t="inlineStr">
-        <is>
-          <t>Only the custodial rails frame a period. Consumer rails are snapshot-only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="112" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Period return / ROI</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRESENT</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRESENT</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRESENT</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRESENT</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRESENT</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRESENT</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>Advisory platforms only (Envestnet, Addepar, Orion)</t>
-        </is>
-      </c>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>Legacy/experimental PerformanceCustom: totalEquityTimeframe, contributions, contributionTimeframe, contributionTimeframeCumulative, withdrawalTimeframe, contributionStreak, dividends, rate-of-return timeframes ALL/1Y/YTD/1M/1W/1D. NOT in the current docs index - confirm availability before designing on it.</t>
-        </is>
-      </c>
-      <c r="J11" s="10" t="inlineStr">
-        <is>
-          <t>Any app showing 'your return' computed it. Document your method or you will not reconcile with the brokerage's own screen.</t>
+      <c r="A5" s="52" t="inlineStr">
+        <is>
+          <t>2 · Calculation Module  —  Pure. Depends on NOTHING — the property that lets it run outside the app.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="44" t="inlineStr">
+        <is>
+          <t>2 · Calculation Module</t>
+        </is>
+      </c>
+      <c r="B6" s="44" t="inlineStr">
+        <is>
+          <t>calculation-module</t>
+        </is>
+      </c>
+      <c r="C6" s="44" t="inlineStr">
+        <is>
+          <t>The engines. Pure — no screens, no store — which is why the module runs outside the app.</t>
+        </is>
+      </c>
+      <c r="D6" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="45" t="inlineStr">
+        <is>
+          <t>— nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="52" t="inlineStr">
+        <is>
+          <t>3 · Features  —  Each owns its own maths, and may use the foundation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="44" t="inlineStr">
+        <is>
+          <t>3 · Features</t>
+        </is>
+      </c>
+      <c r="B8" s="44" t="inlineStr">
+        <is>
+          <t>plan</t>
+        </is>
+      </c>
+      <c r="C8" s="44" t="inlineStr">
+        <is>
+          <t>The retirement simulation, Social Security timing, the odds and the sentences about them.</t>
+        </is>
+      </c>
+      <c r="D8" s="45" t="n">
+        <v>21</v>
+      </c>
+      <c r="E8" s="45" t="n">
+        <v>15</v>
+      </c>
+      <c r="F8" s="46" t="n">
+        <v>16</v>
+      </c>
+      <c r="G8" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="45" t="inlineStr">
+        <is>
+          <t>foundation(27) shared-ui(27) net-worth(11) cash-flow(9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="44" t="inlineStr">
+        <is>
+          <t>3 · Features</t>
+        </is>
+      </c>
+      <c r="B9" s="44" t="inlineStr">
+        <is>
+          <t>cash-flow</t>
+        </is>
+      </c>
+      <c r="C9" s="44" t="inlineStr">
+        <is>
+          <t>Income, tax, spending, the ledger.</t>
+        </is>
+      </c>
+      <c r="D9" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" s="46" t="n">
+        <v>27</v>
+      </c>
+      <c r="G9" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="45" t="inlineStr">
+        <is>
+          <t>foundation(16) setup(7) shared-ui(4) net-worth(3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="44" t="inlineStr">
+        <is>
+          <t>3 · Features</t>
+        </is>
+      </c>
+      <c r="B10" s="44" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="C10" s="44" t="inlineStr">
+        <is>
+          <t>The questions asked at the start, and which ones each person needs.</t>
+        </is>
+      </c>
+      <c r="D10" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="45" t="inlineStr">
+        <is>
+          <t>foundation(12) cash-flow(5) shared-ui(3) plan(2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="44" t="inlineStr">
+        <is>
+          <t>3 · Features</t>
+        </is>
+      </c>
+      <c r="B11" s="44" t="inlineStr">
+        <is>
+          <t>performance</t>
+        </is>
+      </c>
+      <c r="C11" s="44" t="inlineStr">
+        <is>
+          <t>Returns, gains, bonds and yields, the look-back.</t>
+        </is>
+      </c>
+      <c r="D11" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" s="46" t="n">
+        <v>35</v>
+      </c>
+      <c r="G11" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" s="45" t="inlineStr">
+        <is>
+          <t>foundation(17) shared-ui(16) net-worth(13) cash-flow(6)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>POSITION / HOLDING LEVEL</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="9" t="n"/>
-      <c r="G12" s="9" t="n"/>
-      <c r="H12" s="9" t="n"/>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="9" t="n"/>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Holding record</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>holdings[]</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>holdings[]</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>holdings[] + securities[]</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>holdings[]</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>INVPOSLIST / POSSTOCK, POSMF, POSDEBT, POSOPT, POSOTHER</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>holdings[]</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>semt.002 FinInstrmDtls</t>
-        </is>
-      </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>GET /accounts/{id}/positions/all -&gt; results[].instrument, discriminated by instrument.kind</t>
-        </is>
-      </c>
-      <c r="J13" s="10" t="inlineStr">
-        <is>
-          <t>OFX splits the position aggregate by asset class; everyone else uses one record plus a type enum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Security name</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>holdingName</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>holdingName</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>securities.name</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>description / enrichedDescription</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>SECINFO SECNAME</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>description (VERIFY)</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>FinInstrmId/Desc</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>instrument.description</t>
-        </is>
-      </c>
-      <c r="J14" s="10" t="inlineStr">
-        <is>
-          <t>In FDX, holdingName can be the sole identity key - so an unstable string splits a position's history.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>ticker_symbol</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>TICKER</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>symbol (VERIFY)</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>n/a (ID-driven)</t>
-        </is>
-      </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>instrument.symbol (formatted) + instrument.raw_symbol (no exchange suffix)</t>
-        </is>
-      </c>
-      <c r="J15" s="10" t="inlineStr">
-        <is>
-          <t>FDX requires at least one of symbol / securityId+type / holdingName.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>CUSIP / ISIN / SEDOL</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>securityId + securityIdType</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>securityId + securityIdType (CUSIP, ISIN, SEDOL, SICC, VALOR, WKN)</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>cusip, isin, sedol, figi, security_id</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>cusipNumber, isin, sedol</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>SECID UNIQUEID + UNIQUEIDTYPE</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>cusip</t>
-        </is>
-      </c>
-      <c r="H16" s="12" t="inlineStr">
-        <is>
-          <t>FinInstrmId ISIN (primary)</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="n"/>
-      <c r="J16" s="12" t="inlineStr">
-        <is>
-          <t>FDX pairs ID and type in one field pair; Yodlee and Plaid give a named column per scheme. ISIN/CUSIP redistribution is license-gated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="70" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>Asset type</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>holdingType (ANNUITY, BOND, CD, DIGITALASSET, MUTUALFUND, OPTION, OTHER, STOCK) + holdingSubType (CASH, MONEYMARKET)</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>securities.type / subtype</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>securityType (~38 values incl. TIPS, MBS, CMO, STRUCTURED_NOTES, DIGITAL_ASSET); legacy holdingType deprecating</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>POS* aggregate + SECINFO subtype</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>holding_type (VERIFY)</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>CFI code</t>
-        </is>
-      </c>
-      <c r="I17" s="11" t="inlineStr">
-        <is>
-          <t>instrument.kind: stock, etf, mutualfund, cef, adr, crypto, future, option, cfd, other</t>
-        </is>
-      </c>
-      <c r="J17" s="10" t="inlineStr">
-        <is>
-          <t>8 FDX values vs ~38 Yodlee values. Mapping down loses information you cannot recover; mapping up requires a security master.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>quantity (plus contractQuantity, vested/unvested/exercised quantity)</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>UNITS</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>shares (VERIFY)</t>
-        </is>
-      </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>FinInstrmQty</t>
-        </is>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>units - signed (negative = short), fractional supported</t>
-        </is>
-      </c>
-      <c r="J18" s="10" t="inlineStr">
-        <is>
-          <t>Semantics flip by asset class - see Sheet 3. FDX: shares for equity, FACE VALUE for bonds, contracts for options.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Current price</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>currentUnitPrice + currentUnitPriceDate</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>institution_price, close_price</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>UNITPRICE</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>current_price (VERIFY)</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>PricDtls</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>price - last known brokerage price; delayed unless on the real-time plan</t>
-        </is>
-      </c>
-      <c r="J19" s="10" t="inlineStr">
-        <is>
-          <t>Yodlee normalizes bond price; providers may send per-100 or per-unit. Round-trip a bond position before trusting it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>Market value</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>marketValue</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>marketValue</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>institution_value</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>MKTVAL</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>market_value (VERIFY)</t>
-        </is>
-      </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>HldgVal / MT535 :19A::HOLD</t>
-        </is>
-      </c>
-      <c r="I20" s="10" t="inlineStr">
-        <is>
-          <t>Not a field - derive units x price (x multiplier for options/futures) (VERIFY)</t>
-        </is>
-      </c>
-      <c r="J20" s="10" t="inlineStr">
-        <is>
-          <t>Usually the one field everyone agrees on - but check whether accrued interest is inside it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>Face value (bonds)</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>faceValue</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>faceValue (required for bonds; absence implies not a bond)</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>fixed_income object</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>quantity carries face; couponRate separate</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>POSDEBT + DEBTINFO PARVALUE</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>n/a (VERIFY)</t>
-        </is>
-      </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>FaceAmt</t>
-        </is>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>NOT PROVIDED</t>
-        </is>
-      </c>
-      <c r="J21" s="10" t="inlineStr">
-        <is>
-          <t>FDX overloads absence-of-faceValue as a type signal. Fragile.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="70" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>Cost basis</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>taxLots[].costBasis (lot level)</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>taxLots[].costBasis (incl. fees); purchasedPrice at holding level</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>cost_basis (holding); cost_basis per lot</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>costBasis (average cost, incl. commission)</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>INVPOS has no cost basis; derive from INVTRAN history</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>cost_basis (VERIFY)</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>AcqstnPric</t>
-        </is>
-      </c>
-      <c r="I22" s="10" t="inlineStr">
-        <is>
-          <t>average_purchase_price; tax_lots[] (units, purchase price/share, lot cost basis, lot market value, LONG/SHORT) where the institution supports lots; options carry cost basis PER CONTRACT</t>
-        </is>
-      </c>
-      <c r="J22" s="10" t="inlineStr">
-        <is>
-          <t>Three different definitions: lot with fees, holding-average with commission, and price-times-units without fees. Never compare across providers without normalizing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>Purchase price / date</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>purchasedPrice; taxLots[].originalPurchaseDate</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>n/a at holding level</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>n/a (derive from transactions)</t>
-        </is>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>DTPURCHASE (some aggregates)</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>purchase_price (VERIFY)</t>
-        </is>
-      </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>AcqstnDt</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>average_purchase_price; tax lot purchase price (lot acquisition date VERIFY)</t>
-        </is>
-      </c>
-      <c r="J23" s="10" t="inlineStr">
-        <is>
-          <t>Optional almost everywhere; assume missing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="56" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>Long / short</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>taxLots[].positionType (LONG, SHORT)</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>n/a (negative quantity)</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>isShort</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>POSTYPE (LONG, SHORT)</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t>Three encodings: enum, boolean, and sign convention. Sign conventions silently reverse P&amp;L.</t>
-        </is>
-      </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>Sign of units; tax_lots[] position type (LONG, SHORT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>Cash-equivalent flag</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>cashAccount + holdingSubType</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>cashAccount; fiAttributes.isCashEquivalent</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>is_cash_equivalent</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>securityType = CASH / MONEY_MARKET_FUND</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>SUBACCTSEC = CASH</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t>n/a (VERIFY)</t>
-        </is>
-      </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I25" s="10" t="inlineStr">
-        <is>
-          <t>cash_equivalent on mutualfund positions</t>
-        </is>
-      </c>
-      <c r="J25" s="10" t="inlineStr">
-        <is>
-          <t>Determines your denominator for weights and your definition of 'invested assets'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>Coupon rate</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRESENT on holding</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRESENT</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>fixed_income.yield_rate (VERIFY)</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>couponRate</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>DEBTINFO DEBTTYPE, COUPONRT, COUPONFREQ</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t>IntrstRate</t>
-        </is>
-      </c>
-      <c r="I26" s="10" t="inlineStr">
-        <is>
-          <t>NOT PROVIDED</t>
-        </is>
-      </c>
-      <c r="J26" s="10" t="inlineStr">
-        <is>
-          <t>OFX and Yodlee carry it; FDX does not. Bond-heavy portfolios need a security master to fill the hole.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="56" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>Maturity date</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>loanAccount.maturityDate (account level only)</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>fixed_income.maturity_date (VERIFY)</t>
-        </is>
-      </c>
-      <c r="E27" s="10" t="inlineStr">
-        <is>
-          <t>maturityDate (bonds and CDs), term (ISO 8601 period)</t>
-        </is>
-      </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>DEBTINFO DTMAT</t>
-        </is>
-      </c>
-      <c r="G27" s="10" t="inlineStr">
-        <is>
-          <t>maturity_date (VERIFY)</t>
-        </is>
-      </c>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t>MtrtyDt</t>
-        </is>
-      </c>
-      <c r="I27" s="10" t="inlineStr">
-        <is>
-          <t>NOT PROVIDED for bonds. Options: expiration_date, strike_price, option_type, multiplier. Futures: expiration_date, expiration_code, root_symbol, multiplier</t>
-        </is>
-      </c>
-      <c r="J27" s="10" t="inlineStr">
-        <is>
-          <t>FDX has maturityDate for loans, not for bond holdings - a genuine asymmetry in the standard.</t>
+      <c r="A12" s="44" t="inlineStr">
+        <is>
+          <t>3 · Features</t>
+        </is>
+      </c>
+      <c r="B12" s="44" t="inlineStr">
+        <is>
+          <t>net-worth</t>
+        </is>
+      </c>
+      <c r="C12" s="44" t="inlineStr">
+        <is>
+          <t>What you own and owe, how it is classified, and the record of what it was worth.</t>
+        </is>
+      </c>
+      <c r="D12" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" s="46" t="n">
+        <v>41</v>
+      </c>
+      <c r="G12" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" s="45" t="inlineStr">
+        <is>
+          <t>foundation(20) shared-ui(14) plan(6) debt(4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="44" t="inlineStr">
+        <is>
+          <t>3 · Features</t>
+        </is>
+      </c>
+      <c r="B13" s="44" t="inlineStr">
+        <is>
+          <t>accounts</t>
+        </is>
+      </c>
+      <c r="C13" s="44" t="inlineStr">
+        <is>
+          <t>Connecting a broker, importing a file, and one account's own page.</t>
+        </is>
+      </c>
+      <c r="D13" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="46" t="n">
+        <v>16</v>
+      </c>
+      <c r="G13" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="45" t="inlineStr">
+        <is>
+          <t>foundation(15) shared-ui(11) net-worth(7) cash-flow(3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="44" t="inlineStr">
+        <is>
+          <t>3 · Features</t>
+        </is>
+      </c>
+      <c r="B14" s="44" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="C14" s="44" t="inlineStr">
+        <is>
+          <t>What is owed, what it costs, and how long until it clears.</t>
+        </is>
+      </c>
+      <c r="D14" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="45" t="inlineStr">
+        <is>
+          <t>foundation(8) shared-ui(2) plan(2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="44" t="inlineStr">
+        <is>
+          <t>3 · Features</t>
+        </is>
+      </c>
+      <c r="B15" s="44" t="inlineStr">
+        <is>
+          <t>insights</t>
+        </is>
+      </c>
+      <c r="C15" s="44" t="inlineStr">
+        <is>
+          <t>What is worth telling someone, and what is missing from their picture.</t>
+        </is>
+      </c>
+      <c r="D15" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="45" t="inlineStr">
+        <is>
+          <t>net-worth(3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="44" t="inlineStr">
+        <is>
+          <t>3 · Features</t>
+        </is>
+      </c>
+      <c r="B16" s="44" t="inlineStr">
+        <is>
+          <t>goals</t>
+        </is>
+      </c>
+      <c r="C16" s="44" t="inlineStr">
+        <is>
+          <t>What someone is saving toward, and whether they are on track.</t>
+        </is>
+      </c>
+      <c r="D16" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="45" t="inlineStr">
+        <is>
+          <t>foundation(6) shared-ui(4) plan(3) net-worth(1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="52" t="inlineStr">
+        <is>
+          <t>4 · Screens &amp; shared UI  —  May use any module below. Never calculates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="44" t="inlineStr">
+        <is>
+          <t>4 · Screens &amp; shared UI</t>
+        </is>
+      </c>
+      <c r="B18" s="44" t="inlineStr">
+        <is>
+          <t>shared-ui</t>
+        </is>
+      </c>
+      <c r="C18" s="44" t="inlineStr">
+        <is>
+          <t>Components used by more than one module — the gauge, the hero amount, sheets, the keyboard wrapper.</t>
+        </is>
+      </c>
+      <c r="D18" s="45" t="n">
+        <v>86</v>
+      </c>
+      <c r="E18" s="45" t="n">
+        <v>143</v>
+      </c>
+      <c r="F18" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="45" t="inlineStr">
+        <is>
+          <t>foundation(246) plan(88) net-worth(69) cash-flow(67)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="52" t="inlineStr">
+        <is>
+          <t>THE FOLDER MOVE — agreed 2026-08-18, not yet started</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="53" t="inlineStr">
+        <is>
+          <t>Master folder</t>
+        </is>
+      </c>
+      <c r="B21" s="44" t="inlineStr">
+        <is>
+          <t>MoneyKeel-Latest-version/ — one folder per module, holding its maths, screens, components and tests together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="53" t="inlineStr">
+        <is>
+          <t>Import paths</t>
+        </is>
+      </c>
+      <c r="B22" s="44" t="inlineStr">
+        <is>
+          <t>@net-worth/… rather than a trail of ../../, so a file can move within its module without touching anything else.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="53" t="inlineStr">
+        <is>
+          <t>Routes stay put</t>
+        </is>
+      </c>
+      <c r="B23" s="44" t="inlineStr">
+        <is>
+          <t>The files in app/ are one-line re-exports and routing is decided by their path, so they do not move.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="53" t="inlineStr">
+        <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="B24" s="44" t="inlineStr">
+        <is>
+          <t>older-code-&lt;date&gt;/ per RELEASE, matching the build number. Two kept; a third is deleted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="53" t="inlineStr">
+        <is>
+          <t>Fenced THREE ways</t>
+        </is>
+      </c>
+      <c r="B25" s="44" t="inlineStr">
+        <is>
+          <t>Out of the typechecker, out of the test runner and bundler, and a guard test that fails the build if any live file imports from an older-code folder. Without all three, archived code inside the source tree gets compiled, tested, and can be IMPORTED — the stale-code problem arriving through the back door.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="53" t="inlineStr">
+        <is>
+          <t>Move order</t>
+        </is>
+      </c>
+      <c r="B26" s="44" t="inlineStr">
+        <is>
+          <t>One module at a time behind a green suite: debt first (4 source, 4 tests, few dependents), then the small self-contained ones, then net worth, cash flow and plan, then setup, shared UI and foundation last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="53" t="inlineStr">
+        <is>
+          <t>src/ disappears</t>
+        </is>
+      </c>
+      <c r="B27" s="44" t="inlineStr">
+        <is>
+          <t>When the last module leaves. Two places to look is the problem being solved.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Accrued interest / income</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRESENT</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRESENT</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>accruedInterest, accruedIncome</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>ACCRDINT (some aggregates)</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>AcrdIntrstAmt</t>
-        </is>
-      </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>NOT PROVIDED</t>
-        </is>
-      </c>
-      <c r="J28" s="10" t="inlineStr">
-        <is>
-          <t>Yodlee is the only consumer rail that reliably carries it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="42" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>Asset classification</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRESENT</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRESENT</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>sector, industry, market_identifier_code, cfi_code</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>assetClassification[] (type, value, allocation %), securityStyle</t>
-        </is>
-      </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G29" s="10" t="inlineStr">
-        <is>
-          <t>Investment Data Enhancement (product, not field)</t>
-        </is>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>CFI, sector taxonomies</t>
-        </is>
-      </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>NOT PROVIDED (figi_share_class only)</t>
-        </is>
-      </c>
-      <c r="J29" s="10" t="inlineStr">
-        <is>
-          <t>If you need allocation charts, Yodlee ships it and FDX does not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>TRANSACTION LEVEL</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="n"/>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="9" t="n"/>
-      <c r="G30" s="9" t="n"/>
-      <c r="H30" s="9" t="n"/>
-      <c r="I30" s="8" t="n"/>
-      <c r="J30" s="9" t="n"/>
-    </row>
-    <row r="31" ht="56" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>Transaction record</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>investmentTransaction (VERIFY exact schema)</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>/accounts/{id}/transactions</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>investment_transactions[]</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="inlineStr">
-        <is>
-          <t>transaction (container=investment)</t>
-        </is>
-      </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>INVTRANLIST wrapping BUYSTOCK, SELLMF, INCOME, TRANSFER, REINVEST, etc.</t>
-        </is>
-      </c>
-      <c r="G31" s="10" t="inlineStr">
-        <is>
-          <t>transactions[]</t>
-        </is>
-      </c>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t>semt.017 / MT536 statement of transactions</t>
-        </is>
-      </c>
-      <c r="I31" s="10" t="inlineStr">
-        <is>
-          <t>GET /accounts/{id}/activities - only position-changing transactions, daily refresh, often full history since inception. Orders endpoint is the intraday/pending view.</t>
-        </is>
-      </c>
-      <c r="J31" s="10" t="inlineStr">
-        <is>
-          <t>OFX is the most explicit: a distinct aggregate per action, so intent is unambiguous.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="84" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>Transaction type</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>transactionType + subType (VERIFY enums)</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>type + subtype (buy, sell, cash, transfer, fee, dividend...)</t>
-        </is>
-      </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>baseType, type, categoryType</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>aggregate name + BUYTYPE/SELLTYPE/INCOMETYPE</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
-        <is>
-          <t>type / category</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>TrnsTp</t>
-        </is>
-      </c>
-      <c r="I32" s="10" t="inlineStr">
-        <is>
-          <t>type - predefined common types (BUY, SELL, DIVIDEND, CONTRIBUTION, WITHDRAWAL, FEE...); when unmapped, SnapTrade passes through the BROKERAGE'S OWN string. Docs advise relying on amount/units/price rather than the type.</t>
-        </is>
-      </c>
-      <c r="J32" s="10" t="inlineStr">
-        <is>
-          <t>THE integration risk. This taxonomy alone decides contribution vs income vs internal transfer, and therefore your entire return number.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>Trade / posted date</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>tradeDate, settlementDate, postedTimestamp (VERIFY)</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>postedTimestamp (filter key for startTime/endTime)</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="E33" s="10" t="inlineStr">
-        <is>
-          <t>date, transactionDate, postDate</t>
-        </is>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>DTTRADE, DTSETTLE, DTPOSTED</t>
-        </is>
-      </c>
-      <c r="G33" s="10" t="inlineStr">
-        <is>
-          <t>date / posted_at</t>
-        </is>
-      </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>TradDt, SttlmDt</t>
-        </is>
-      </c>
-      <c r="I33" s="10" t="inlineStr">
-        <is>
-          <t>trade_date, settlement_date (VERIFY); activities may carry date only, no timestamp</t>
-        </is>
-      </c>
-      <c r="J33" s="10" t="inlineStr">
-        <is>
-          <t>Filtering on posted date while weighting flows by trade date shifts Modified Dietz weights.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="56" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>Units / price / amount</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>units, unitPrice, total (VERIFY)</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>quantity, price, amount</t>
-        </is>
-      </c>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>quantity, price, amount</t>
-        </is>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>UNITS, UNITPRICE, TOTAL</t>
-        </is>
-      </c>
-      <c r="G34" s="10" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="H34" s="10" t="inlineStr">
-        <is>
-          <t>Qty, DealPric, SttlmAmt</t>
-        </is>
-      </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>units, price, amount - documented sign convention: amount positive = cash in, negative = cash out; BUY = +units / -amount, SELL = -units / +amount</t>
-        </is>
-      </c>
-      <c r="J34" s="10" t="inlineStr">
-        <is>
-          <t>Sign conventions for buys vs sells differ; normalize to a signed cash-flow model early.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>Fees / commission</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>fees, commission (VERIFY)</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>fees</t>
-        </is>
-      </c>
-      <c r="E35" s="10" t="inlineStr">
-        <is>
-          <t>commission, fee</t>
-        </is>
-      </c>
-      <c r="F35" s="10" t="inlineStr">
-        <is>
-          <t>COMMISSION, FEES, LOAD, TAXES</t>
-        </is>
-      </c>
-      <c r="G35" s="10" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>ChrgsDtls</t>
-        </is>
-      </c>
-      <c r="I35" s="10" t="inlineStr">
-        <is>
-          <t>fee (VERIFY)</t>
-        </is>
-      </c>
-      <c r="J35" s="10" t="inlineStr">
-        <is>
-          <t>FDX carries fees on transactions but not on holdings - the reason cost basis diverges.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>Income type</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>subType (VERIFY)</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>subtype (dividend, interest, qualified dividend...)</t>
-        </is>
-      </c>
-      <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t>INCOMETYPE (CGLONG, CGSHORT, DIV, INTEREST, MISC)</t>
-        </is>
-      </c>
-      <c r="G36" s="10" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I36" s="10" t="inlineStr">
-        <is>
-          <t>type = DIVIDEND / INTEREST; option_symbol present on option activities</t>
-        </is>
-      </c>
-      <c r="J36" s="10" t="inlineStr">
-        <is>
-          <t>OFX distinguishes long vs short capital gains distributions natively; most others do not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="56" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>Unrealized gain/loss (P&amp;L)</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRESENT (derive: marketValue - costBasis)</t>
-        </is>
-      </c>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRESENT</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="inlineStr">
-        <is>
-          <t>n/a (derive)</t>
-        </is>
-      </c>
-      <c r="E37" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRESENT (derive from costBasis and value)</t>
-        </is>
-      </c>
-      <c r="F37" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRESENT</t>
-        </is>
-      </c>
-      <c r="G37" s="10" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H37" s="10" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I37" s="11" t="inlineStr">
-        <is>
-          <t>open_pnl - profit/loss since the position was opened. Docs recommend deriving it yourself from average_purchase_price x units vs current price.</t>
-        </is>
-      </c>
-      <c r="J37" s="10" t="inlineStr">
-        <is>
-          <t>One of the few consumer rails that ships a P&amp;L field directly - but it is a derived brokerage number, so it will not tie to your own calculation.</t>
+      <c r="A28" s="53" t="inlineStr">
+        <is>
+          <t>Worth knowing</t>
+        </is>
+      </c>
+      <c r="B28" s="44" t="inlineStr">
+        <is>
+          <t>git already keeps every version forever. The archive folders earn their place by being VISIBLE without a command, but they sit on top of the real history rather than being it — which is why keeping two is safe.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="B25:I25"/>
+    <mergeCell ref="B24:I24"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="B28:I28"/>
+    <mergeCell ref="B22:I22"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="B26:I26"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="56" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="17" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Per-asset-class fields and semantic traps</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Quantity and price semantics change meaning by class within the same field name. This is where most reconciliation breaks appear.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Asset class</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Type value (FDX / Yodlee)</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Quantity means</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Price means</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Income event</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>Class-specific fields</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>Trap</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>Common stock</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>STOCK / COMMON_STOCK</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>Shares</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>Per share</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>Dividend (cash or reinvested)</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>Stock splits arrive as a transaction in OFX (SPLIT) but may just appear as a changed quantity elsewhere. Unreconciled splits look like a 100% return.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>ETF</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>STOCK / EXCHANGE_TRADED_FUND</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Shares</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>Per share</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>Distribution</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>FDX has no ETF value - ETFs collapse into STOCK or MUTUALFUND depending on the provider. Breaks asset-class reporting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Mutual fund</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>MUTUALFUND / MUTUAL_FUND</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>Shares (fractional)</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>NAV, daily</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>Dividend + capital gain distribution</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>NAV is stale intraday. A same-day 'return' on a fund is noise. OFX separates CGLONG/CGSHORT; FDX does not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Money market / cash</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>OTHER + holdingSubType MONEYMARKET or CASH / MONEY_MARKET_FUND, CASH</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Units at ~1.00</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>Interest</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>cashAccount flag, fiAttributes.isCashEquivalent</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>FDX requires holdingType=OTHER with a subtype - not a first-class type. If cashAccount and holdingSubType disagree, Plaid rejects the holding.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="84" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Bond (corporate, muni, govt, TIPS, MBS, CMO)</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>BOND / CORPORATE_BOND, MUNICIPAL_BOND, GOVERNMENT_BOND, TIPS, MORTGAGE_BACKED_SECURITY, COLLATERALIZED_MORTGAGE_OBLIGATION</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>FACE VALUE in FDX; normalized quantity in Yodlee</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>Per 100 of par, or per unit - provider-dependent</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>Coupon (interest), accrual between payments</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>faceValue (FDX); couponRate, maturityDate, term, accruedInterest (Yodlee); COUPONRT, COUPONFREQ, DTMAT, PARVALUE (OFX)</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>The worst class for divergence. FDX gives you faceValue and nothing else - no coupon, no maturity, no accrual on the holding. You cannot compute yield or income from FDX alone.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>CD</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>CD / CERTIFICATE_OF_DEPOSIT</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Face / principal</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Par</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>Interest</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>interestRate, maturityDate, term (Yodlee)</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>May be modelled as a deposit account OR an investment holding by the same institution. Deduplicate at household level.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Option</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>OPTION / CALL_OPTION, PUT_OPTION</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>CONTRACTS, not shares</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Per contract or per share - check the multiplier</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>strikePrice, expirationDate, optionType (Yodlee); OPTINFO OPTTYPE, STRIKEPRICE, DTEXPIRE, SHPERCTRCT (OFX)</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>The 100x multiplier is not always in the payload. Market value that is 100x off is the classic symptom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Crypto / digital asset</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>DIGITALASSET / DIGITAL_ASSET (accountType DIGITAL_WALLET)</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Tokens, up to 16 significant digits in Yodlee, 8-18 dp on-chain</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>Per token, 24/7 pricing</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>Staking rewards (often typed as income or as a buy)</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>Precision loss is the failure mode: a float pipeline destroys satoshi-level balances. Use decimals end to end. Also: 24/7 pricing means your 'as-of' and 'previous close' concepts break.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Commodity</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>OTHER / COMMODITY</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>Contract quantity; Yodlee notes quantity does NOT apply</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>Per contract</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>contractQuantity (Yodlee)</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>FDX has no commodity type. Everything lands in OTHER and you lose the class.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Currency / FX</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>OTHER / CURRENCY</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Contract quantity</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Rate</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>contractQuantity; per-holding currency object (FDX)</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>FDX allows a holding-level currency that differs from the account. If you ignore it, you sum yen and dollars.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>Annuity / variable life</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>ANNUITY / ANNUITY_FUND, VARIABLE_ANNUITY</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>Unit value</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>Credited interest</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>Yodlee surfaces these under the insurance container too</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>Plaid treats annuity and insurance accounts as discoverable-only - listed but no balances or transactions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="56" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>Equity comp (RSU, RSA, ESO, performance units)</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>no FDX value / RESTRICTED_STOCK_UNIT, RESTRICTED_STOCK_AWARD, EMPLOYEE_STOCK_OPTION</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Yodlee splits vested / unvested / exercised</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>Market price</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>None until vest or exercise</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>vestedQuantity, unvestedQuantity, vestedValue, unvestedValue, vestedSharesExercisable, exercisedQuantity, vestingDate, grantDate, spread, strikePrice (all Yodlee)</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>Yodlee is far richer here than FDX. Including unvested value in net worth or in return is a material misstatement - decide explicitly.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="82" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="17" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Gaps, workarounds, and the decisions you must make explicitly</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Gap / decision</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Why it matters for your 10-day view</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>What to do</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>No historical valuation in any consumer standard</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Beginning value at T-10 simply is not retrievable. Every metric on Sheet 1 that needs BMV depends on state you own.</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Snapshot holdings and cash daily on connection and persist them. Treat your snapshot store as the system of record for performance; treat the API as the system of record for current position.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>No performance field anywhere on the consumer rails</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>You will show a return number the brokerage's own app shows differently.</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>Pick one method (Modified Dietz for short windows, chain-linked TWR once you have a daily series), label it in the UI, and keep an IRR alongside for the 'what did I earn' question.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Transaction taxonomy is the real integration cost</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>Whether a $5,000 movement is a contribution, a dividend reinvestment, or an internal transfer changes your return, not just a label.</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Build a canonical transaction taxonomy with four axes: direction (in/out), externality (external flow vs internal), economic nature (principal vs income vs fee vs tax), and security-affecting (yes/no). Map every provider enum into it, and keep the raw provider value on the record forever.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Three incompatible cost-basis definitions</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>Unrealized gain differs across providers for the same position.</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>Store cost basis with a provenance tag (lot-with-fees / average-with-commission / derived-price-x-units) and never mix tags in one rollup.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Bond and fixed-income data is thin in FDX</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>No coupon, no maturity, no accrual on the holding - so no yield, no income projection.</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Plan for a security master (or Yodlee/OFX where available) as a required input, not an enhancement. Enrich by ISIN/CUSIP; fall back to a name match only with a confidence flag.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Security identity is not stable</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>FDX allows holdingName as the sole identifier; a spacing change forks a position's history. Plaid's security_id can change on a corporate action.</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>Resolve to your own internal security key with a documented precedence (ISIN &gt; CUSIP &gt; SEDOL &gt; ticker+exchange &gt; normalized name) and persist the alias chain.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Asset-type enums do not map cleanly</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>FDX's 8 holding types vs Yodlee's ~38 security types. ETFs, commodities, and equity comp have no FDX home.</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Model your own class taxonomy at the granularity of your product, map upward from the widest source, and store the source enum verbatim for audit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>As-of timestamps are unnormalized and often stale</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>A 10-day return computed against a mispriced endpoint is unfalsifiable and wrong.</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Reject or flag any valuation older than your tolerance; do not silently substitute the last known price. FDX does not normalize timezone - normalize on ingest.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Corporate actions are inconsistently transmitted</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Splits, spinoffs, and mergers appear as typed transactions in OFX, and sometimes as nothing at all elsewhere.</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Detect unexplained quantity changes (quantity delta with no matching transaction) and quarantine rather than booking a phantom gain.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Fees are partly invisible</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>Advisory and wrap fees are sometimes netted into NAV or unit price before you ever see them.</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>Report gross and net where you can separate them, and disclose when you cannot.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Holding-level currency can differ from account currency in FDX.</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Store amount + currency as one type. Never sum bare numbers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>Precision</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>Crypto needs 8-18 decimals; a float pipeline loses balances silently.</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>Decimal end to end, including your database columns and your JSON serialization.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>Lookback limits</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Transaction history is commonly 12-24 months, and 'startTime' behavior varies by provider.</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Backfill fully at first connection, persist everything, and never re-derive history from a live call.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>1033 landscape</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>The CFPB Personal Financial Data Rights rule pushed FDX toward being the de facto US standard, so FDX's omissions become industry-wide omissions.</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>Do not wait for the standard to add performance fields. Assume derivation is permanently your job, and design the snapshot store as core infrastructure rather than a cache.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="74" customWidth="1" min="2" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="17" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>SnapTrade - how it compares to the FDX-family rails</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Brokerage-direct, trading-first, and the only source examined that natively names contributions, withdrawals, and rate of return - though those endpoints are legacy or experimental.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>What SnapTrade does</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Implication</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>WHERE SNAPTRADE IS STRUCTURALLY DIFFERENT</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n"/>
-      <c r="C5" s="9" t="n"/>
-    </row>
-    <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Not an FDX implementation</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>SnapTrade is brokerage-direct and trading-first (Robinhood, Schwab, Fidelity, IBKR, crypto venues), not a 1033/FDX data-sharing rail. Its schema owes nothing to FDX and everything to broker order-management models.</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Do not expect FDX field names or FDX certification semantics. Map it as its own source, not as an FDX variant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>It ships P&amp;L</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>open_pnl on each position - profit or loss since the position was opened. FDX, Plaid Core Exchange, and MX ship no P&amp;L field at all.</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>Useful for display parity with the broker's own app. Do not mix it into your own computed gain - the broker's basis convention is not yours. SnapTrade's own docs suggest deriving from average_purchase_price.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>It has a historical value endpoint</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>getAccountBalanceHistory returns estimated historical total account value (positions + cash). This is the only consumer-rail approximation of your T-10 beginning value that I found.</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Experimental, disabled by default, capped lookback, and estimated. Use it to bootstrap a new connection's history; do not make it the basis of a headline return. Keep your own daily snapshot as the system of record.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>It once had a performance API</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>A PerformanceCustom schema exists in the SDK spec: totalEquityTimeframe, contributions, contributionTimeframe, contributionTimeframeCumulative, withdrawalTimeframe, contributionStreak, dividends, plus rate-of-return timeframes ALL / 1Y / YTD / 1M / 1W / 1D.</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>This is exactly your requested vocabulary - beginning value series, contributions, withdrawals, ROI over a period - and no other rail names these concepts natively. But it is absent from the current documentation index, so treat it as legacy or experimental and confirm availability with SnapTrade before you design a product around it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Asset-class coverage is the widest</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>instrument.kind discriminates stock, etf, mutualfund, cef, adr, crypto, future, option, cfd, other - with option and future contract metadata (strike, expiration, multiplier) and CFD wrappers.</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Your ETF, crypto, commodity/futures, and option requirements are all first-class here, where FDX collapses them into STOCK or OTHER. This is the strongest argument for SnapTrade as your investment source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Transaction history is deeper</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Activities often cover the full account history since inception, and are explicitly typed for buys, sells, dividends, contributions, withdrawals.</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>This is what makes Modified Dietz and XIRR feasible over long windows. Plaid/Yodlee lookback is typically 12-24 months.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>WHERE IT IS WEAKER THAN THE FDX RAILS</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>No CUSIP or ISIN</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>Identity is a SnapTrade UUID plus symbol, exchange MIC, and FIGI (figi_code, figi_share_class).</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>If your security master keys on CUSIP/ISIN, you need a FIGI-to-CUSIP bridge. FIGI is free and unlicensed, which is arguably an advantage - but it is a different join key.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Fixed income is thin to absent</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>No face value, no coupon, no maturity, no accrued interest on positions.</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Worse than Yodlee and OFX for bonds and CDs. If bonds matter, SnapTrade is not your fixed-income source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>No market value field</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>Positions carry units and price, not a value. Options and futures carry a multiplier.</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>Derive value yourself and apply the multiplier. Forgetting it produces the classic 100x option error.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>No asset classification</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>No sector, asset class, or style taxonomy (Yodlee ships all three).</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Buy or build classification for allocation and drift views.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>Price freshness is plan-dependent</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>Real-time only on the real-time plan; otherwise cached daily with a per-brokerage 'Cache Expiry Time'. Manual refresh available.</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>Do not compute a same-day return on daily-cached prices. Their own docs recommend a third-party market data provider for pricing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>Type fallback to raw broker strings</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>When an activity type does not fit SnapTrade's common types, it passes through the brokerage's own label verbatim.</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Your canonical taxonomy needs an explicit unmapped bucket plus alerting, not a silent default. Their guidance - lean on amount, units, price, and sign convention rather than the type string - is the right instinct and worth adopting across all your sources.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Coverage is brokerage-by-brokerage</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>Tax lots, real-time data, and trading are each enabled per institution.</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Feature availability is a per-connection attribute in your data model, not a global flag.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>HOW TO POSITION IT IN YOUR STACK</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-    </row>
-    <row r="21" ht="56" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>Recommended split</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>SnapTrade for brokerage and crypto depth (positions, full activity history, options/futures, P&amp;L, trading). An FDX rail (Plaid Core Exchange / Akoya / MX) for bank, card, loan, and 1033-covered breadth. Yodlee or a security master for fixed income, accrual, and classification.</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>Your canonical model absorbs all three. Keep provider, raw type string, and raw identifiers on every record so any normalization decision stays reversible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>What does not change</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>Even with SnapTrade, contributions, withdrawals, and return over your 10-day window are yours to derive from activities plus your own snapshot series - unless the performance endpoints prove to be live and supported.</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>The daily snapshot store remains core infrastructure. SnapTrade shortens the backfill; it does not remove the requirement.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24723,4 +22929,2528 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J37"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Field-name crosswalk by data element</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>'NOT PRESENT' means the standard does not transmit it at all. 'VERIFY' means the name comes from documentation summaries, not a field-level read of the licensed spec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Data element</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>FDX v6.x (canonical)</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Plaid Core Exchange (provider side, FDX subset)</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Plaid Investments (recipient side)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Yodlee v1.1</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>OFX 2.x</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>MX Platform</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>ISO 20022 / SWIFT MT</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>SnapTrade (brokerage-direct)</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Divergence risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>ACCOUNT LEVEL</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="n"/>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="9" t="n"/>
+      <c r="I5" s="8" t="n"/>
+      <c r="J5" s="9" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Account container</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>investmentAccount</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>investmentAccount</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>accounts[] (type=investment)</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>account (container=investment)</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>INVSTMTRS / INVACCTFROM</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>account (type INVESTMENT)</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>semt.002 AcctSubLvl / MT535 :97a::SAFE</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>GET /accounts -&gt; account object (id UUID, institution_name, balance.total)</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>FDX nests by account-type key; Yodlee uses a flat 'container' discriminator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Total account value</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>currentValue</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>currentValue</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>balances.current</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>balance / currentBalance</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>INVBAL + position values</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>semt.002 TtlHldgsVal</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>account.balance.total.amount + .currency (VERIFY)</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>FDX splits total investments (currentValue) from cash (availableCashBalance); Yodlee 'balance' semantics vary by provider. Do not assume additivity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Cash / sweep balance</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>availableCashBalance</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>availableCashBalance</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>balances.available</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>cash / availableCash</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>INVBAL AVAILCASH, BUYPOWER</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>available_balance</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>GET /accounts/{id}/balances -&gt; cash, buying_power, per currency</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>'Available cash' at a broker can include margin buying power. Treat buying power as a distinct concept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Valuation as-of timestamp</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>balanceAsOf</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>balanceAsOf</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>close_price_as_of / update_datetime</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>lastUpdated</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>DTASOF</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>balance_updated_at (VERIFY)</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>semt.002 StmtGnlDtls/StmtDtTm</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>sync_status.holdings.last_successful_sync (VERIFY); per-brokerage 'Cache Expiry Time'; real-time only on the real-time plan</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>The single most abused field. FDX does not normalize timezone; a local time labelled Z is read as UTC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Beginning-of-period value</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>NOT PRESENT</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>NOT PRESENT</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>NOT PRESENT</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>NOT PRESENT</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>NOT PRESENT</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>NOT PRESENT</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>semt.003 previous statement / MT535 prior report</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>getAccountBalanceHistory - historical total account value (positions + cash). EXPERIMENTAL, disabled by default, capped lookback.</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>Only the custodial rails frame a period. Consumer rails are snapshot-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="112" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Period return / ROI</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>NOT PRESENT</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>NOT PRESENT</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>NOT PRESENT</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>NOT PRESENT</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>NOT PRESENT</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>NOT PRESENT</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Advisory platforms only (Envestnet, Addepar, Orion)</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>Legacy/experimental PerformanceCustom: totalEquityTimeframe, contributions, contributionTimeframe, contributionTimeframeCumulative, withdrawalTimeframe, contributionStreak, dividends, rate-of-return timeframes ALL/1Y/YTD/1M/1W/1D. NOT in the current docs index - confirm availability before designing on it.</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>Any app showing 'your return' computed it. Document your method or you will not reconcile with the brokerage's own screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>POSITION / HOLDING LEVEL</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="9" t="n"/>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="9" t="n"/>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Holding record</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>holdings[]</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>holdings[]</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>holdings[] + securities[]</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>holdings[]</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>INVPOSLIST / POSSTOCK, POSMF, POSDEBT, POSOPT, POSOTHER</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>holdings[]</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>semt.002 FinInstrmDtls</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>GET /accounts/{id}/positions/all -&gt; results[].instrument, discriminated by instrument.kind</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>OFX splits the position aggregate by asset class; everyone else uses one record plus a type enum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Security name</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>holdingName</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>holdingName</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>securities.name</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>description / enrichedDescription</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>SECINFO SECNAME</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>description (VERIFY)</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>FinInstrmId/Desc</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>instrument.description</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>In FDX, holdingName can be the sole identity key - so an unstable string splits a position's history.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>ticker_symbol</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>TICKER</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>symbol (VERIFY)</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>n/a (ID-driven)</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>instrument.symbol (formatted) + instrument.raw_symbol (no exchange suffix)</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>FDX requires at least one of symbol / securityId+type / holdingName.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>CUSIP / ISIN / SEDOL</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>securityId + securityIdType</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>securityId + securityIdType (CUSIP, ISIN, SEDOL, SICC, VALOR, WKN)</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>cusip, isin, sedol, figi, security_id</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>cusipNumber, isin, sedol</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>SECID UNIQUEID + UNIQUEIDTYPE</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>cusip</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>FinInstrmId ISIN (primary)</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>FDX pairs ID and type in one field pair; Yodlee and Plaid give a named column per scheme. ISIN/CUSIP redistribution is license-gated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="70" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Asset type</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>holdingType (ANNUITY, BOND, CD, DIGITALASSET, MUTUALFUND, OPTION, OTHER, STOCK) + holdingSubType (CASH, MONEYMARKET)</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>securities.type / subtype</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>securityType (~38 values incl. TIPS, MBS, CMO, STRUCTURED_NOTES, DIGITAL_ASSET); legacy holdingType deprecating</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>POS* aggregate + SECINFO subtype</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>holding_type (VERIFY)</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>CFI code</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>instrument.kind: stock, etf, mutualfund, cef, adr, crypto, future, option, cfd, other</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>8 FDX values vs ~38 Yodlee values. Mapping down loses information you cannot recover; mapping up requires a security master.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>quantity (plus contractQuantity, vested/unvested/exercised quantity)</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>UNITS</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>shares (VERIFY)</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>FinInstrmQty</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>units - signed (negative = short), fractional supported</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>Semantics flip by asset class - see Sheet 3. FDX: shares for equity, FACE VALUE for bonds, contracts for options.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Current price</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>currentUnitPrice + currentUnitPriceDate</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>institution_price, close_price</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>UNITPRICE</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>current_price (VERIFY)</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>PricDtls</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>price - last known brokerage price; delayed unless on the real-time plan</t>
+        </is>
+      </c>
+      <c r="J19" s="10" t="inlineStr">
+        <is>
+          <t>Yodlee normalizes bond price; providers may send per-100 or per-unit. Round-trip a bond position before trusting it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Market value</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>marketValue</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>marketValue</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>institution_value</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>MKTVAL</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>market_value (VERIFY)</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>HldgVal / MT535 :19A::HOLD</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Not a field - derive units x price (x multiplier for options/futures) (VERIFY)</t>
+        </is>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>Usually the one field everyone agrees on - but check whether accrued interest is inside it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Face value (bonds)</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>faceValue</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>faceValue (required for bonds; absence implies not a bond)</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>fixed_income object</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>quantity carries face; couponRate separate</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>POSDEBT + DEBTINFO PARVALUE</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>n/a (VERIFY)</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>FaceAmt</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>NOT PROVIDED</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>FDX overloads absence-of-faceValue as a type signal. Fragile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="70" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Cost basis</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>taxLots[].costBasis (lot level)</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>taxLots[].costBasis (incl. fees); purchasedPrice at holding level</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>cost_basis (holding); cost_basis per lot</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>costBasis (average cost, incl. commission)</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>INVPOS has no cost basis; derive from INVTRAN history</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>cost_basis (VERIFY)</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>AcqstnPric</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>average_purchase_price; tax_lots[] (units, purchase price/share, lot cost basis, lot market value, LONG/SHORT) where the institution supports lots; options carry cost basis PER CONTRACT</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>Three different definitions: lot with fees, holding-average with commission, and price-times-units without fees. Never compare across providers without normalizing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Purchase price / date</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>purchasedPrice; taxLots[].originalPurchaseDate</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>n/a at holding level</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>n/a (derive from transactions)</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>DTPURCHASE (some aggregates)</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>purchase_price (VERIFY)</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>AcqstnDt</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>average_purchase_price; tax lot purchase price (lot acquisition date VERIFY)</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>Optional almost everywhere; assume missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="56" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Long / short</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>taxLots[].positionType (LONG, SHORT)</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>n/a (negative quantity)</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>isShort</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>POSTYPE (LONG, SHORT)</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>Three encodings: enum, boolean, and sign convention. Sign conventions silently reverse P&amp;L.</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Sign of units; tax_lots[] position type (LONG, SHORT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Cash-equivalent flag</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>cashAccount + holdingSubType</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>cashAccount; fiAttributes.isCashEquivalent</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>is_cash_equivalent</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>securityType = CASH / MONEY_MARKET_FUND</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>SUBACCTSEC = CASH</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>n/a (VERIFY)</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>cash_equivalent on mutualfund positions</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>Determines your denominator for weights and your definition of 'invested assets'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Coupon rate</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>NOT PRESENT on holding</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>NOT PRESENT</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>fixed_income.yield_rate (VERIFY)</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>couponRate</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>DEBTINFO DEBTTYPE, COUPONRT, COUPONFREQ</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>IntrstRate</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>NOT PROVIDED</t>
+        </is>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>OFX and Yodlee carry it; FDX does not. Bond-heavy portfolios need a security master to fill the hole.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="56" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Maturity date</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>loanAccount.maturityDate (account level only)</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>fixed_income.maturity_date (VERIFY)</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>maturityDate (bonds and CDs), term (ISO 8601 period)</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>DEBTINFO DTMAT</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>maturity_date (VERIFY)</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>MtrtyDt</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>NOT PROVIDED for bonds. Options: expiration_date, strike_price, option_type, multiplier. Futures: expiration_date, expiration_code, root_symbol, multiplier</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>FDX has maturityDate for loans, not for bond holdings - a genuine asymmetry in the standard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Accrued interest / income</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>NOT PRESENT</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>NOT PRESENT</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>accruedInterest, accruedIncome</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>ACCRDINT (some aggregates)</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>AcrdIntrstAmt</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>NOT PROVIDED</t>
+        </is>
+      </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>Yodlee is the only consumer rail that reliably carries it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Asset classification</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>NOT PRESENT</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>NOT PRESENT</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>sector, industry, market_identifier_code, cfi_code</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>assetClassification[] (type, value, allocation %), securityStyle</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>Investment Data Enhancement (product, not field)</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>CFI, sector taxonomies</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>NOT PROVIDED (figi_share_class only)</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>If you need allocation charts, Yodlee ships it and FDX does not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>TRANSACTION LEVEL</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="9" t="n"/>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="9" t="n"/>
+      <c r="I30" s="8" t="n"/>
+      <c r="J30" s="9" t="n"/>
+    </row>
+    <row r="31" ht="56" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Transaction record</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>investmentTransaction (VERIFY exact schema)</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>/accounts/{id}/transactions</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>investment_transactions[]</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>transaction (container=investment)</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>INVTRANLIST wrapping BUYSTOCK, SELLMF, INCOME, TRANSFER, REINVEST, etc.</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>transactions[]</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>semt.017 / MT536 statement of transactions</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>GET /accounts/{id}/activities - only position-changing transactions, daily refresh, often full history since inception. Orders endpoint is the intraday/pending view.</t>
+        </is>
+      </c>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>OFX is the most explicit: a distinct aggregate per action, so intent is unambiguous.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="84" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Transaction type</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>transactionType + subType (VERIFY enums)</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>type + subtype (buy, sell, cash, transfer, fee, dividend...)</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>baseType, type, categoryType</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>aggregate name + BUYTYPE/SELLTYPE/INCOMETYPE</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>type / category</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>TrnsTp</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>type - predefined common types (BUY, SELL, DIVIDEND, CONTRIBUTION, WITHDRAWAL, FEE...); when unmapped, SnapTrade passes through the BROKERAGE'S OWN string. Docs advise relying on amount/units/price rather than the type.</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>THE integration risk. This taxonomy alone decides contribution vs income vs internal transfer, and therefore your entire return number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Trade / posted date</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>tradeDate, settlementDate, postedTimestamp (VERIFY)</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>postedTimestamp (filter key for startTime/endTime)</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>date, transactionDate, postDate</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>DTTRADE, DTSETTLE, DTPOSTED</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>date / posted_at</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>TradDt, SttlmDt</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>trade_date, settlement_date (VERIFY); activities may carry date only, no timestamp</t>
+        </is>
+      </c>
+      <c r="J33" s="10" t="inlineStr">
+        <is>
+          <t>Filtering on posted date while weighting flows by trade date shifts Modified Dietz weights.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="56" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Units / price / amount</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>units, unitPrice, total (VERIFY)</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>quantity, price, amount</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>quantity, price, amount</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>UNITS, UNITPRICE, TOTAL</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>Qty, DealPric, SttlmAmt</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>units, price, amount - documented sign convention: amount positive = cash in, negative = cash out; BUY = +units / -amount, SELL = -units / +amount</t>
+        </is>
+      </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>Sign conventions for buys vs sells differ; normalize to a signed cash-flow model early.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>Fees / commission</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>fees, commission (VERIFY)</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>fees</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>commission, fee</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>COMMISSION, FEES, LOAD, TAXES</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>ChrgsDtls</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>fee (VERIFY)</t>
+        </is>
+      </c>
+      <c r="J35" s="10" t="inlineStr">
+        <is>
+          <t>FDX carries fees on transactions but not on holdings - the reason cost basis diverges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>Income type</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>subType (VERIFY)</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>subtype (dividend, interest, qualified dividend...)</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>INCOMETYPE (CGLONG, CGSHORT, DIV, INTEREST, MISC)</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>type = DIVIDEND / INTEREST; option_symbol present on option activities</t>
+        </is>
+      </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>OFX distinguishes long vs short capital gains distributions natively; most others do not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="56" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Unrealized gain/loss (P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>NOT PRESENT (derive: marketValue - costBasis)</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>NOT PRESENT</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>n/a (derive)</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>NOT PRESENT (derive from costBasis and value)</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>NOT PRESENT</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>open_pnl - profit/loss since the position was opened. Docs recommend deriving it yourself from average_purchase_price x units vs current price.</t>
+        </is>
+      </c>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>One of the few consumer rails that ships a P&amp;L field directly - but it is a derived brokerage number, so it will not tie to your own calculation.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Per-asset-class fields and semantic traps</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Quantity and price semantics change meaning by class within the same field name. This is where most reconciliation breaks appear.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Asset class</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Type value (FDX / Yodlee)</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Quantity means</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Price means</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Income event</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Class-specific fields</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Trap</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Common stock</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>STOCK / COMMON_STOCK</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Per share</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Dividend (cash or reinvested)</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Stock splits arrive as a transaction in OFX (SPLIT) but may just appear as a changed quantity elsewhere. Unreconciled splits look like a 100% return.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>ETF</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>STOCK / EXCHANGE_TRADED_FUND</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Per share</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>FDX has no ETF value - ETFs collapse into STOCK or MUTUALFUND depending on the provider. Breaks asset-class reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Mutual fund</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>MUTUALFUND / MUTUAL_FUND</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Shares (fractional)</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>NAV, daily</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Dividend + capital gain distribution</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>NAV is stale intraday. A same-day 'return' on a fund is noise. OFX separates CGLONG/CGSHORT; FDX does not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Money market / cash</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>OTHER + holdingSubType MONEYMARKET or CASH / MONEY_MARKET_FUND, CASH</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Units at ~1.00</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>cashAccount flag, fiAttributes.isCashEquivalent</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>FDX requires holdingType=OTHER with a subtype - not a first-class type. If cashAccount and holdingSubType disagree, Plaid rejects the holding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="84" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Bond (corporate, muni, govt, TIPS, MBS, CMO)</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>BOND / CORPORATE_BOND, MUNICIPAL_BOND, GOVERNMENT_BOND, TIPS, MORTGAGE_BACKED_SECURITY, COLLATERALIZED_MORTGAGE_OBLIGATION</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>FACE VALUE in FDX; normalized quantity in Yodlee</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Per 100 of par, or per unit - provider-dependent</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Coupon (interest), accrual between payments</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>faceValue (FDX); couponRate, maturityDate, term, accruedInterest (Yodlee); COUPONRT, COUPONFREQ, DTMAT, PARVALUE (OFX)</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>The worst class for divergence. FDX gives you faceValue and nothing else - no coupon, no maturity, no accrual on the holding. You cannot compute yield or income from FDX alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>CD / CERTIFICATE_OF_DEPOSIT</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Face / principal</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Par</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>interestRate, maturityDate, term (Yodlee)</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>May be modelled as a deposit account OR an investment holding by the same institution. Deduplicate at household level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>OPTION / CALL_OPTION, PUT_OPTION</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>CONTRACTS, not shares</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Per contract or per share - check the multiplier</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>strikePrice, expirationDate, optionType (Yodlee); OPTINFO OPTTYPE, STRIKEPRICE, DTEXPIRE, SHPERCTRCT (OFX)</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>The 100x multiplier is not always in the payload. Market value that is 100x off is the classic symptom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Crypto / digital asset</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>DIGITALASSET / DIGITAL_ASSET (accountType DIGITAL_WALLET)</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Tokens, up to 16 significant digits in Yodlee, 8-18 dp on-chain</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Per token, 24/7 pricing</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Staking rewards (often typed as income or as a buy)</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Precision loss is the failure mode: a float pipeline destroys satoshi-level balances. Use decimals end to end. Also: 24/7 pricing means your 'as-of' and 'previous close' concepts break.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>OTHER / COMMODITY</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Contract quantity; Yodlee notes quantity does NOT apply</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Per contract</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>contractQuantity (Yodlee)</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>FDX has no commodity type. Everything lands in OTHER and you lose the class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Currency / FX</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>OTHER / CURRENCY</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Contract quantity</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>contractQuantity; per-holding currency object (FDX)</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>FDX allows a holding-level currency that differs from the account. If you ignore it, you sum yen and dollars.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Annuity / variable life</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>ANNUITY / ANNUITY_FUND, VARIABLE_ANNUITY</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Unit value</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>Credited interest</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>Yodlee surfaces these under the insurance container too</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Plaid treats annuity and insurance accounts as discoverable-only - listed but no balances or transactions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Equity comp (RSU, RSA, ESO, performance units)</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>no FDX value / RESTRICTED_STOCK_UNIT, RESTRICTED_STOCK_AWARD, EMPLOYEE_STOCK_OPTION</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Yodlee splits vested / unvested / exercised</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Market price</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>None until vest or exercise</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>vestedQuantity, unvestedQuantity, vestedValue, unvestedValue, vestedSharesExercisable, exercisedQuantity, vestingDate, grantDate, spread, strikePrice (all Yodlee)</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Yodlee is far richer here than FDX. Including unvested value in net worth or in return is a material misstatement - decide explicitly.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17" customHeight="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Cost basis - three definitions, one decision table</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Named on the Gaps tab, resolved here. The three are not interchangeable and the weakest is the one MoneyKeel currently holds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="B4" s="34" t="inlineStr">
+        <is>
+          <t>What it includes</t>
+        </is>
+      </c>
+      <c r="C4" s="34" t="inlineStr">
+        <is>
+          <t>Who gives you this</t>
+        </is>
+      </c>
+      <c r="D4" s="34" t="inlineStr">
+        <is>
+          <t>Worth for tax reporting</t>
+        </is>
+      </c>
+      <c r="E4" s="34" t="inlineStr">
+        <is>
+          <t>What it does to unrealised gain</t>
+        </is>
+      </c>
+      <c r="F4" s="34" t="inlineStr">
+        <is>
+          <t>What the screen must say when this is all you hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="35" t="inlineStr">
+        <is>
+          <t>THE THREE DEFINITIONS</t>
+        </is>
+      </c>
+      <c r="B5" s="35" t="n"/>
+      <c r="C5" s="35" t="n"/>
+      <c r="D5" s="35" t="n"/>
+      <c r="E5" s="35" t="n"/>
+      <c r="F5" s="35" t="n"/>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="36" t="inlineStr">
+        <is>
+          <t>Lot-level, fees included</t>
+        </is>
+      </c>
+      <c r="B6" s="36" t="inlineStr">
+        <is>
+          <t>Each batch of shares, its own purchase date and price, with commission and fees added in. Adjusted over time by reinvested income (up) and return of capital (down).</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>FDX taxLots[].costBasis and Plaid Core Exchange taxLots[] where the institution supports lots; SnapTrade tax_lots[] where the institution supports lots. Both of MoneyKeel's live brokers sent NONE.</t>
+        </is>
+      </c>
+      <c r="D6" s="36" t="inlineStr">
+        <is>
+          <t>The only one that can produce a defensible long-versus-short split, because only it holds a real purchase date per batch. Still an estimate: the broker's own 1099-B is what the IRS sees.</t>
+        </is>
+      </c>
+      <c r="E6" s="36" t="inlineStr">
+        <is>
+          <t>Correct, and correct per batch - which is what a person needs when deciding which shares to sell.</t>
+        </is>
+      </c>
+      <c r="F6" s="36" t="inlineStr">
+        <is>
+          <t>Nothing special. Say which lots the figures came from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="36" t="inlineStr">
+        <is>
+          <t>Holding average, commission included</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="inlineStr">
+        <is>
+          <t>One average cost per share across the whole position, with commission in. No purchase dates.</t>
+        </is>
+      </c>
+      <c r="C7" s="36" t="inlineStr">
+        <is>
+          <t>Yodlee costBasis. SnapTrade average_purchase_price (whether fees are inside is per broker - UNKNOWN in general).</t>
+        </is>
+      </c>
+      <c r="D7" s="36" t="inlineStr">
+        <is>
+          <t>Enough for a total gain figure. CANNOT split long from short, because there is no purchase date to judge. Mutual funds are commonly held this way by the broker too, so for funds this often matches what the broker reports.</t>
+        </is>
+      </c>
+      <c r="E7" s="36" t="inlineStr">
+        <is>
+          <t>Correct in total, meaningless per batch.</t>
+        </is>
+      </c>
+      <c r="F7" s="36" t="inlineStr">
+        <is>
+          <t>'This is an average across all your shares - we cannot tell which were bought when, so we cannot split the tax treatment.' Then show no long-versus-short split at all rather than a guessed one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="36" t="inlineStr">
+        <is>
+          <t>Price x units, fees excluded</t>
+        </is>
+      </c>
+      <c r="B8" s="36" t="inlineStr">
+        <is>
+          <t>Units multiplied by a purchase price. No commission, no fees, no adjustments.</t>
+        </is>
+      </c>
+      <c r="C8" s="36" t="inlineStr">
+        <is>
+          <t>What you get when you derive basis from FDX purchasedPrice x units - FDX carries NO fee field on a holding. This is MoneyKeel's current position: one synthetic lot built from an average price.</t>
+        </is>
+      </c>
+      <c r="D8" s="36" t="inlineStr">
+        <is>
+          <t>Weakest. It understates cost, so it OVERSTATES gain and overstates the tax owed. Never present it as a tax figure.</t>
+        </is>
+      </c>
+      <c r="E8" s="36" t="inlineStr">
+        <is>
+          <t>Overstates the gain by the fees paid, and by every reinvested distribution not added back.</t>
+        </is>
+      </c>
+      <c r="F8" s="36" t="inlineStr">
+        <is>
+          <t>'Estimated from the average price we were given. It does not include trading costs, so your real gain is likely smaller than this.' This is MoneyKeel's live state today and the sentence is missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>THE DECISION</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="n"/>
+      <c r="C9" s="35" t="n"/>
+      <c r="D9" s="35" t="n"/>
+      <c r="E9" s="35" t="n"/>
+      <c r="F9" s="35" t="n"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="36" t="inlineStr">
+        <is>
+          <t>Store the tag, not just the number</t>
+        </is>
+      </c>
+      <c r="B10" s="36" t="inlineStr">
+        <is>
+          <t>Every basis figure carries which of the three it is, and where it came from. Two figures with different tags are never added, compared, or shown in the same total without saying so.</t>
+        </is>
+      </c>
+      <c r="C10" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="A11" s="36" t="inlineStr">
+        <is>
+          <t>Rank, and fall back downward only</t>
+        </is>
+      </c>
+      <c r="B11" s="36" t="inlineStr">
+        <is>
+          <t>Lot-with-fees beats holding-average beats price-x-units. Take the best available per holding, per broker - not one choice for the whole app - and never upgrade a weaker figure by inventing the missing part.</t>
+        </is>
+      </c>
+      <c r="C11" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="98" customHeight="1">
+      <c r="A12" s="36" t="inlineStr">
+        <is>
+          <t>Basis is not static</t>
+        </is>
+      </c>
+      <c r="B12" s="36" t="inlineStr">
+        <is>
+          <t>Whatever the source, the app must adjust it as events arrive: reinvested income increases it, return of capital reduces it, a split leaves the total unchanged but changes it per share, an in-kind transfer must carry it across. A basis copied once from a broker and never adjusted drifts furthest for the long-held fund positions this audience has most of.</t>
+        </is>
+      </c>
+      <c r="C12" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E12" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="84" customHeight="1">
+      <c r="A13" s="36" t="inlineStr">
+        <is>
+          <t>What the person sees</t>
+        </is>
+      </c>
+      <c r="B13" s="36" t="inlineStr">
+        <is>
+          <t>One line under every gain figure naming the weakest ingredient in it. A retiree does not need the word 'provenance'; they need to know whether the number is good enough to act on. 'Good enough to see how you're doing, not good enough for your tax return' is the honest version, and it is true for all three definitions.</t>
+        </is>
+      </c>
+      <c r="C13" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E13" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Calculation Module/MoneyKeel-calculation-master-v1.xlsx
+++ b/Calculation Module/MoneyKeel-calculation-master-v1.xlsx
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -11871,10 +11871,12 @@
       </c>
       <c r="F84" s="44" t="inlineStr">
         <is>
-          <t>WHY IT IS NOT ONE SUM. Nobody knows what markets will do. A plan that assumes exactly 6% every year for thirty years gives one confident answer that is certainly wrong. So instead the app plays out your life 400 times, giving each year a different random return — some good, some terrible, averaging out to what your mix of accounts would normally earn.
+          <t>WHY IT IS NOT ONE SUM. Nobody knows what markets will do. A plan that assumes exactly 6% every year for thirty years gives one confident answer that is certainly wrong. So instead the app plays out your life 1,000 times, giving each year a different random return — some good, some terrible, averaging out to what your mix of accounts would normally earn.
 EACH RUN GOES LIKE THIS. Start with what you have. Every year until you retire: the pot grows or shrinks by that year's random return, your saving goes in, and any big planned cost comes out. From retirement on: your spending comes out, your pension and Social Security go in, and whatever is left keeps growing. If the money outlasts you, that run worked.
-Do that 400 times and count. 340 worked out of 400 → 85%.
-WHAT 85% MEANS. Not "you will have 85% of what you need". It means that in 85 out of 100 possible futures, the money lasted — and in 15, it ran out. It is a measure of how much room for bad luck you have.
+Do that 1,000 times and count. It lasted in 770 of 1,000 (77%). Rounded to the nearest 5 → 75%. A real 100 (all 1,000 lasted) shows 100%; a real 0 shows 0%; rounding never creates them — 98% shows as 95, never 100.
+WHAT 75% MEANS. Not "you will have 75% of what you need". It means that in 75 out of 100 possible futures, the money lasted — and in 25, it ran out. It is a measure of how much room for bad luck you have.
+THE RECOMMENDED NEST EGG, in the same breath. Alongside the odds this reports a target pot: 25 x the yearly spending your guaranteed income does not cover, measured in the dollars of your retirement year. Worked: spending $6,000 a month at retirement is $72,000 a year; Social Security of $2,600 a month is $31,200; the yearly gap is $40,800; 25 x that is $1,020,000. The 25 comes from the old rule of thumb that a pot lasts if you draw about 4% of it a year (25 = 1 / 4%). It is a YARDSTICK, deliberately crude: it ignores how long you plan for and what your money earns. The odds figure is the real answer; this is the number the "to close the gap" line is measured against.
+BOTH GUARANTEED-INCOME RULES APPLY HERE. Social Security rises with inflation; a pension stays flat. Your own withdrawals are never counted as guaranteed income — the run works those out.
 THE ONE RULE THAT IS EASY TO GET WRONG. Your SPENDING rises with inflation — groceries in 2040 cost more than groceries today. But your MORTGAGE PAYMENT DOES NOT. A fixed payment is the same dollars every year until the loan ends. Treating it like groceries would overstate what it costs you every single year, and then stop overstating it the moment it ends.
 It is repeatable: the same plan always gives the same percentage, today and tomorrow.</t>
         </is>
@@ -14624,12 +14626,18 @@
       </c>
       <c r="E117" s="44" t="inlineStr">
         <is>
-          <t>What will the pot be worth at retirement?  Answer: a dollar figure, with a range around it.</t>
+          <t>What will the pot be worth at retirement, and how big does it need to be? Answer: two dollar figures — what you will have, and the target pot that pays for the whole plan.</t>
         </is>
       </c>
       <c r="F117" s="44" t="inlineStr">
         <is>
-          <t>The same year-by-year growth as the simulation, run over the years to retirement, reporting where the runs land. It answers "how much will I have", where the simulation answers "will it last".</t>
+          <t>TWO FIGURES, no random runs anywhere in this one — it is the straight-line check beside the 1,000-run odds.
+WHAT YOU WILL HAVE. Today's pot grown at your expected return for the years until you retire, plus every year's saving grown for however many years it has left. Worked at 6%: $600,000 today over 7 years becomes $902,000; $24,000 saved each of those years adds about $201,000; $1,103,000 in all.
+WHAT YOU WILL NEED — the target pot. Walk every retirement year one at a time, from the year you retire to the age you plan to. In each year: take that year's spending, take off the guaranteed income you receive that year, and that difference is what the pot must hand you. Bring each of those amounts back to a retirement-year value by dividing by your expected return once for every year you have to wait for it. Add them all up. That total is the pot that pays for the whole plan.
+Two rules ride along: spending rises with inflation every year, and so does Social Security, but a pension stays flat.
+WHY THE NUMBER IS SMALLER THAN THE SUM OF THE SPENDING. Money you do not need until year fifteen keeps earning until then, so you need less than fifteen years' spending set aside today.
+MONEY IS NEEDED AT THE START OF ITS YEAR. The first retirement year's spending is not discounted at all — January's groceries cannot be paid out of December's growth. Some published calculators charge each year at its END, which gives every year one more year of growth and reports a target about (1 + return) / (1 + inflation) smaller — roughly 3% lower at a 6% return and 2.5% inflation. Neither is wrong; ours is the cautious side, and the difference is a timing convention, not a disagreement about the arithmetic.
+HOW IT DIFFERS FROM THE 25 x YARDSTICK reported by the odds engine: this one knows how long you plan for and what your money earns; the yardstick knows neither.</t>
         </is>
       </c>
       <c r="G117" s="44" t="inlineStr">
@@ -20201,10 +20209,10 @@
         </is>
       </c>
       <c r="D18" s="45" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E18" s="45" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F18" s="44" t="inlineStr">
         <is>
@@ -20223,7 +20231,7 @@
       </c>
       <c r="I18" s="45" t="inlineStr">
         <is>
-          <t>foundation(236) plan(91) net-worth(67) cash-flow(67)</t>
+          <t>foundation(236) plan(93) cash-flow(68) net-worth(67)</t>
         </is>
       </c>
     </row>

--- a/Calculation Module/MoneyKeel-calculation-master-v1.xlsx
+++ b/Calculation Module/MoneyKeel-calculation-master-v1.xlsx
@@ -7,17 +7,18 @@
   </bookViews>
   <sheets>
     <sheet name="0. Read Me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1. Metrics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2. Engines" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3. Work list" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="4. Architecture" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="5. Transaction taxonomy" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="6. Field crosswalk" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="7. By asset class" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="8. Cost basis" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="9. Snapshot &amp; honesty" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="10. Gaps &amp; decisions" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="11. SnapTrade" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="1. Your decisions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="1. Metrics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2. Engines" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="3. Work list" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="4. Architecture" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="5. Transaction taxonomy" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="6. Field crosswalk" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="7. By asset class" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="8. Cost basis" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="9. Snapshot &amp; honesty" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="10. Gaps &amp; decisions" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="11. SnapTrade" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -285,7 +286,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -411,11 +412,55 @@
         <color rgb="00DDDDDD"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -556,6 +601,9 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1121,6 +1169,321 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17" customHeight="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Cost basis - three definitions, one decision table</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Named on the Gaps tab, resolved here. The three are not interchangeable and the weakest is the one MoneyKeel currently holds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="B4" s="34" t="inlineStr">
+        <is>
+          <t>What it includes</t>
+        </is>
+      </c>
+      <c r="C4" s="34" t="inlineStr">
+        <is>
+          <t>Who gives you this</t>
+        </is>
+      </c>
+      <c r="D4" s="34" t="inlineStr">
+        <is>
+          <t>Worth for tax reporting</t>
+        </is>
+      </c>
+      <c r="E4" s="34" t="inlineStr">
+        <is>
+          <t>What it does to unrealised gain</t>
+        </is>
+      </c>
+      <c r="F4" s="34" t="inlineStr">
+        <is>
+          <t>What the screen must say when this is all you hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="35" t="inlineStr">
+        <is>
+          <t>THE THREE DEFINITIONS</t>
+        </is>
+      </c>
+      <c r="B5" s="35" t="n"/>
+      <c r="C5" s="35" t="n"/>
+      <c r="D5" s="35" t="n"/>
+      <c r="E5" s="35" t="n"/>
+      <c r="F5" s="35" t="n"/>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="36" t="inlineStr">
+        <is>
+          <t>Lot-level, fees included</t>
+        </is>
+      </c>
+      <c r="B6" s="36" t="inlineStr">
+        <is>
+          <t>Each batch of shares, its own purchase date and price, with commission and fees added in. Adjusted over time by reinvested income (up) and return of capital (down).</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>FDX taxLots[].costBasis and Plaid Core Exchange taxLots[] where the institution supports lots; SnapTrade tax_lots[] where the institution supports lots. Both of MoneyKeel's live brokers sent NONE.</t>
+        </is>
+      </c>
+      <c r="D6" s="36" t="inlineStr">
+        <is>
+          <t>The only one that can produce a defensible long-versus-short split, because only it holds a real purchase date per batch. Still an estimate: the broker's own 1099-B is what the IRS sees.</t>
+        </is>
+      </c>
+      <c r="E6" s="36" t="inlineStr">
+        <is>
+          <t>Correct, and correct per batch - which is what a person needs when deciding which shares to sell.</t>
+        </is>
+      </c>
+      <c r="F6" s="36" t="inlineStr">
+        <is>
+          <t>Nothing special. Say which lots the figures came from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="36" t="inlineStr">
+        <is>
+          <t>Holding average, commission included</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="inlineStr">
+        <is>
+          <t>One average cost per share across the whole position, with commission in. No purchase dates.</t>
+        </is>
+      </c>
+      <c r="C7" s="36" t="inlineStr">
+        <is>
+          <t>Yodlee costBasis. SnapTrade average_purchase_price (whether fees are inside is per broker - UNKNOWN in general).</t>
+        </is>
+      </c>
+      <c r="D7" s="36" t="inlineStr">
+        <is>
+          <t>Enough for a total gain figure. CANNOT split long from short, because there is no purchase date to judge. Mutual funds are commonly held this way by the broker too, so for funds this often matches what the broker reports.</t>
+        </is>
+      </c>
+      <c r="E7" s="36" t="inlineStr">
+        <is>
+          <t>Correct in total, meaningless per batch.</t>
+        </is>
+      </c>
+      <c r="F7" s="36" t="inlineStr">
+        <is>
+          <t>'This is an average across all your shares - we cannot tell which were bought when, so we cannot split the tax treatment.' Then show no long-versus-short split at all rather than a guessed one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="36" t="inlineStr">
+        <is>
+          <t>Price x units, fees excluded</t>
+        </is>
+      </c>
+      <c r="B8" s="36" t="inlineStr">
+        <is>
+          <t>Units multiplied by a purchase price. No commission, no fees, no adjustments.</t>
+        </is>
+      </c>
+      <c r="C8" s="36" t="inlineStr">
+        <is>
+          <t>What you get when you derive basis from FDX purchasedPrice x units - FDX carries NO fee field on a holding. This is MoneyKeel's current position: one synthetic lot built from an average price.</t>
+        </is>
+      </c>
+      <c r="D8" s="36" t="inlineStr">
+        <is>
+          <t>Weakest. It understates cost, so it OVERSTATES gain and overstates the tax owed. Never present it as a tax figure.</t>
+        </is>
+      </c>
+      <c r="E8" s="36" t="inlineStr">
+        <is>
+          <t>Overstates the gain by the fees paid, and by every reinvested distribution not added back.</t>
+        </is>
+      </c>
+      <c r="F8" s="36" t="inlineStr">
+        <is>
+          <t>'Estimated from the average price we were given. It does not include trading costs, so your real gain is likely smaller than this.' This is MoneyKeel's live state today and the sentence is missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>THE DECISION</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="n"/>
+      <c r="C9" s="35" t="n"/>
+      <c r="D9" s="35" t="n"/>
+      <c r="E9" s="35" t="n"/>
+      <c r="F9" s="35" t="n"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="36" t="inlineStr">
+        <is>
+          <t>Store the tag, not just the number</t>
+        </is>
+      </c>
+      <c r="B10" s="36" t="inlineStr">
+        <is>
+          <t>Every basis figure carries which of the three it is, and where it came from. Two figures with different tags are never added, compared, or shown in the same total without saying so.</t>
+        </is>
+      </c>
+      <c r="C10" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="A11" s="36" t="inlineStr">
+        <is>
+          <t>Rank, and fall back downward only</t>
+        </is>
+      </c>
+      <c r="B11" s="36" t="inlineStr">
+        <is>
+          <t>Lot-with-fees beats holding-average beats price-x-units. Take the best available per holding, per broker - not one choice for the whole app - and never upgrade a weaker figure by inventing the missing part.</t>
+        </is>
+      </c>
+      <c r="C11" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="98" customHeight="1">
+      <c r="A12" s="36" t="inlineStr">
+        <is>
+          <t>Basis is not static</t>
+        </is>
+      </c>
+      <c r="B12" s="36" t="inlineStr">
+        <is>
+          <t>Whatever the source, the app must adjust it as events arrive: reinvested income increases it, return of capital reduces it, a split leaves the total unchanged but changes it per share, an in-kind transfer must carry it across. A basis copied once from a broker and never adjusted drifts furthest for the long-held fund positions this audience has most of.</t>
+        </is>
+      </c>
+      <c r="C12" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E12" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="84" customHeight="1">
+      <c r="A13" s="36" t="inlineStr">
+        <is>
+          <t>What the person sees</t>
+        </is>
+      </c>
+      <c r="B13" s="36" t="inlineStr">
+        <is>
+          <t>One line under every gain figure naming the weakest ingredient in it. A retiree does not need the word 'provenance'; they need to know whether the number is good enough to act on. 'Good enough to see how you're doing, not good enough for your tax return' is the honest version, and it is true for all three definitions.</t>
+        </is>
+      </c>
+      <c r="C13" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E13" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
@@ -1421,7 +1784,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1702,7 +2065,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2034,6 +2397,2637 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00085041"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G79"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="66" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="56" customHeight="1">
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>YOUR DECISIONS — every metric you graded in METRICS-DELIVERABLE-ANSWERED-2026-08-20.xlsx, in YOUR order, with YOUR verdict and YOUR new formula, and what now serves it in the code. 72 metrics · 56 questions answered. GENERATED from your own file on every build, so this tab cannot drift from what you decided. 'NOT YET MAPPED' means the decomposition grid for that metric cites no engine name, no function and no source file that exists on the Engines tab — the gap is shown, never hidden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="43" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B2" s="43" t="inlineStr">
+        <is>
+          <t>Metric — your name for it</t>
+        </is>
+      </c>
+      <c r="C2" s="43" t="inlineStr">
+        <is>
+          <t>Use cases you graded</t>
+        </is>
+      </c>
+      <c r="D2" s="43" t="inlineStr">
+        <is>
+          <t>YOUR VERDICT</t>
+        </is>
+      </c>
+      <c r="E2" s="43" t="inlineStr">
+        <is>
+          <t>YOUR NEW FORMULA (column K, first use case)</t>
+        </is>
+      </c>
+      <c r="F2" s="43" t="inlineStr">
+        <is>
+          <t>What serves it in the code now</t>
+        </is>
+      </c>
+      <c r="G2" s="43" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="54" t="inlineStr">
+        <is>
+          <t>SECTION A</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B4" s="44" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C4" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D4" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E4" s="44" t="inlineStr">
+        <is>
+          <t>Compute total assets minus total debts from the accounts that HAVE values, and name the gap: "Does not include Chase checking — no balance yet." Never put a silent $0 in the total; a silent zero reads as a loss (master tab 1 row 52 column K). The person supplies it by typing a balance or re-running the connection.</t>
+        </is>
+      </c>
+      <c r="F4" s="44" t="inlineStr">
+        <is>
+          <t>DEBTS_FROM_SETUP · DEBT_ACTUAL_TOTAL · DEBT_MINIMUM_TOTAL · DEBT_PAYMENTS_ACTUAL · DEBT_PICTURE · DEBT_REQUIRED_PAYMENT (+8 more)</t>
+        </is>
+      </c>
+      <c r="G4" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 14 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" s="44" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="C5" s="44" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="44" t="inlineStr">
+        <is>
+          <t>Same as Net worth P1-A.</t>
+        </is>
+      </c>
+      <c r="F5" s="44" t="inlineStr">
+        <is>
+          <t>ALLOCATION_BY_HOLDING_KIND</t>
+        </is>
+      </c>
+      <c r="G5" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 1 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B6" s="44" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="C6" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D6" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E6" s="44" t="inlineStr">
+        <is>
+          <t>List it by name with no number and label the total: "at least $X — Amex balance not entered." A total that silently omits a known debt overstates net worth in the direction that hurts most. The person supplies it from the latest statement.</t>
+        </is>
+      </c>
+      <c r="F6" s="44" t="inlineStr">
+        <is>
+          <t>ACCOUNTS_FROM_SETUP · ACCOUNT_NAMES · ACCOUNT_SHARE_OF_TOTAL · ACCOUNT_SPLIT · ACCOUNT_TYPE_FACTS · ALLOCATION_BY_CLASS (+35 more)</t>
+        </is>
+      </c>
+      <c r="G6" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 41 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B7" s="44" t="inlineStr">
+        <is>
+          <t>Liquid net worth</t>
+        </is>
+      </c>
+      <c r="C7" s="44" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E7" s="44" t="inlineStr">
+        <is>
+          <t>Default each account's tag from its class — cash: same-day; listed stocks and funds: days; CDs and bonds: at maturity or sale; property: years — SHOW the assumed tag on each account, editable. The headline carries the assumption: "assumes brokerage holdings can be sold within days." A person can correct a visible assumption; nobody can correct a hidden one.</t>
+        </is>
+      </c>
+      <c r="F7" s="44" t="inlineStr">
+        <is>
+          <t>ACCOUNTS_FROM_SETUP · ACCOUNT_NAMES · ACCOUNT_SHARE_OF_TOTAL · ACCOUNT_SPLIT · ACCOUNT_TYPE_FACTS · ALLOCATION_BY_CLASS (+35 more)</t>
+        </is>
+      </c>
+      <c r="G7" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 41 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B8" s="44" t="inlineStr">
+        <is>
+          <t>Investable assets</t>
+        </is>
+      </c>
+      <c r="C8" s="44" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="44" t="inlineStr">
+        <is>
+          <t>It lands in Unclassified, which the investments total already includes (master tab 2 row 122) — so the denominator holds it. Flag when the Unclassified share is material (threshold: founder call, open question 12).</t>
+        </is>
+      </c>
+      <c r="F8" s="44" t="inlineStr">
+        <is>
+          <t>ALLOCATION_BY_HOLDING_KIND · TOTAL_CASH · TOTAL_INVESTABLE</t>
+        </is>
+      </c>
+      <c r="G8" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 3 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B9" s="44" t="inlineStr">
+        <is>
+          <t>Home equity</t>
+        </is>
+      </c>
+      <c r="C9" s="44" t="n">
+        <v>12</v>
+      </c>
+      <c r="D9" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="44" t="inlineStr">
+        <is>
+          <t>No home-equity line at all. If a mortgage exists without a home value, show the debt and one ask: "Add what you think the house is worth to see your equity." Never infer a value from the mortgage size.</t>
+        </is>
+      </c>
+      <c r="F9" s="44" t="inlineStr">
+        <is>
+          <t>ACCOUNTS_FROM_SETUP · ACCOUNT_NAMES · ACCOUNT_SHARE_OF_TOTAL · ACCOUNT_SPLIT · ACCOUNT_TYPE_FACTS · ALLOCATION_BY_CLASS (+25 more)</t>
+        </is>
+      </c>
+      <c r="G9" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 31 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B10" s="44" t="inlineStr">
+        <is>
+          <t>Real estate and physical assets</t>
+        </is>
+      </c>
+      <c r="C10" s="44" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E10" s="44" t="inlineStr">
+        <is>
+          <t>Listed by name, no number, one ask. Same rule as every missing balance: named absence beats silent zero (Net worth P1-A).</t>
+        </is>
+      </c>
+      <c r="F10" s="44" t="inlineStr">
+        <is>
+          <t>ACCOUNTS_FROM_SETUP · ACCOUNT_NAMES · ACCOUNT_SHARE_OF_TOTAL · ACCOUNT_SPLIT · ACCOUNT_TYPE_FACTS · ALLOCATION_BY_CLASS (+25 more)</t>
+        </is>
+      </c>
+      <c r="G10" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 31 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B11" s="44" t="inlineStr">
+        <is>
+          <t>Debt detail: rate, term, payoff date</t>
+        </is>
+      </c>
+      <c r="C11" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D11" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="44" t="inlineStr">
+        <is>
+          <t>Refuse the date; ask for the rate from the statement. Same rule as Total liabilities P2-A — never a silent default rate.</t>
+        </is>
+      </c>
+      <c r="F11" s="44" t="inlineStr">
+        <is>
+          <t>DEBTS_FROM_SETUP · DEBT_ACTUAL_TOTAL · DEBT_MINIMUM_TOTAL · DEBT_PAYMENTS_ACTUAL · DEBT_PICTURE · DEBT_REQUIRED_PAYMENT (+4 more)</t>
+        </is>
+      </c>
+      <c r="G11" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 10 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B12" s="44" t="inlineStr">
+        <is>
+          <t>Weighted average cost of debt</t>
+        </is>
+      </c>
+      <c r="C12" s="44" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="44" t="inlineStr">
+        <is>
+          <t>Compute Sum(balance × rate) ÷ (the balances WITH rates), and say the coverage: "6.1%, based on the $210,000 of your $260,000 debt with known rates." Excluding from numerator only, while keeping the full denominator, would fake a lower rate — both sides shrink together.</t>
+        </is>
+      </c>
+      <c r="F12" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="48" t="inlineStr">
+        <is>
+          <t>NOT YET MAPPED</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B13" s="44" t="inlineStr">
+        <is>
+          <t>Leverage and coverage ratios</t>
+        </is>
+      </c>
+      <c r="C13" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D13" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E13" s="44" t="inlineStr">
+        <is>
+          <t>The ratio inherits Net worth P1-A and Total liabilities P1-A: compute on what is known, name the gap, and suppress the ratio when a MATERIAL side is missing — a ratio with a named hole in its denominator misleads more than no ratio.</t>
+        </is>
+      </c>
+      <c r="F13" s="44" t="inlineStr">
+        <is>
+          <t>DEBTS_FROM_SETUP · DEBT_ACTUAL_TOTAL · DEBT_MINIMUM_TOTAL · DEBT_PAYMENTS_ACTUAL · DEBT_PICTURE · DEBT_REQUIRED_PAYMENT (+4 more)</t>
+        </is>
+      </c>
+      <c r="G13" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 10 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B14" s="44" t="inlineStr">
+        <is>
+          <t>Allocation by asset class</t>
+        </is>
+      </c>
+      <c r="C14" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D14" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E14" s="44" t="inlineStr">
+        <is>
+          <t>An explicit, visible Unclassified slice — never spread across other slices, never dropped (master tab 1 rows 38 and 46 column K). The identity: slices sum exactly to total assets (ALLOCATION_BY_CLASS, master tab 2 row 138).</t>
+        </is>
+      </c>
+      <c r="F14" s="44" t="inlineStr">
+        <is>
+          <t>ACCOUNT_SPLIT · ALLOCATION_BY_CLASS · SLICE_WORDING</t>
+        </is>
+      </c>
+      <c r="G14" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 3 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B15" s="44" t="inlineStr">
+        <is>
+          <t>Allocation by tax treatment</t>
+        </is>
+      </c>
+      <c r="C15" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D15" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="44" t="inlineStr">
+        <is>
+          <t>No institution tells us this reliably — it is always the person's own answer (TAX_TREATMENT, master tab 2 row 33). The engine defaults unknown to TAXABLE, the cautious side for tax owed — but for SEQUENCING advice a mislabeled account gives wrong advice, so: accounts still unconfirmed sit in a visible "confirm how this is taxed" state and sequencing output is suppressed until the material ones are confirmed.</t>
+        </is>
+      </c>
+      <c r="F15" s="44" t="inlineStr">
+        <is>
+          <t>TAX_TREATMENT</t>
+        </is>
+      </c>
+      <c r="G15" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 1 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B16" s="44" t="inlineStr">
+        <is>
+          <t>Allocation by liquidity</t>
+        </is>
+      </c>
+      <c r="C16" s="44" t="n">
+        <v>12</v>
+      </c>
+      <c r="D16" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="44" t="inlineStr">
+        <is>
+          <t>Same defaulting rule as Liquid net worth P1-A: class-based default tags into buckets — same-day / days / months / years — visible and editable per account (founder to bless the defaulting, open question 4).</t>
+        </is>
+      </c>
+      <c r="F16" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="48" t="inlineStr">
+        <is>
+          <t>NOT YET MAPPED</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B17" s="44" t="inlineStr">
+        <is>
+          <t>Concentration</t>
+        </is>
+      </c>
+      <c r="C17" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D17" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E17" s="44" t="inlineStr">
+        <is>
+          <t>Its weight is unknowable — and so is everyone else's, because the denominator is wrong. Suppress the concentration figure and name the blocker: "we could not price LCTX, so shares of your total can't be computed." Never rank around a hole.</t>
+        </is>
+      </c>
+      <c r="F17" s="44" t="inlineStr">
+        <is>
+          <t>CONCENTRATION</t>
+        </is>
+      </c>
+      <c r="G17" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 1 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B18" s="44" t="inlineStr">
+        <is>
+          <t>Embedded tax on unrealised gains</t>
+        </is>
+      </c>
+      <c r="C18" s="44" t="n">
+        <v>12</v>
+      </c>
+      <c r="D18" s="48" t="inlineStr">
+        <is>
+          <t>CUT</t>
+        </is>
+      </c>
+      <c r="E18" s="44" t="inlineStr">
+        <is>
+          <t>No basis → NO gain figure and NO embedded-tax line for that holding: "We don't know what you paid for this. Add it from a statement and we'll show your gain." The current engine's rule — a lot with no cost contributes zero to basis while its shares still count (HOLDING_COST_BASIS, master tab 2 row 64) — makes gain = value − partial basis, which OVERSTATES gain and tax; for a tax figure that is the wrong direction to be wrong in (master tab 8 row D8). No quantity → we cannot even verify the value; show the stated value only, no gain, and ask for share count from the statement. The household after-tax total then carries: "excludes holdings where cost is unknown ($X of value)".</t>
+        </is>
+      </c>
+      <c r="F18" s="44" t="inlineStr">
+        <is>
+          <t>grid: section-A.md whole section · code: the estimated-tax display on Holding detail; the dead portfolio-level compute on Performance. Realised-gains math and drawdown tax treatment are different, kept concepts</t>
+        </is>
+      </c>
+      <c r="G18" s="46" t="inlineStr">
+        <is>
+          <t>CUT — removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B19" s="44" t="inlineStr">
+        <is>
+          <t>Currency exposure</t>
+        </is>
+      </c>
+      <c r="C19" s="44" t="n">
+        <v>12</v>
+      </c>
+      <c r="D19" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="44" t="inlineStr">
+        <is>
+          <t>Exclude it from the dollar total and show it in its own currency with a named line: "¥1,200,000 — no exchange rate available, not in your total." Summing yen and dollars is the failure this metric exists to prevent (spine row 21 trap).</t>
+        </is>
+      </c>
+      <c r="F19" s="44" t="inlineStr">
+        <is>
+          <t>ALLOCATION_BY_HOLDING_KIND · CURRENCY</t>
+        </is>
+      </c>
+      <c r="G19" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 2 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B20" s="44" t="inlineStr">
+        <is>
+          <t>Net worth data quality</t>
+        </is>
+      </c>
+      <c r="C20" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D20" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E20" s="44" t="inlineStr">
+        <is>
+          <t>Count it as typed — the cautious side for a trust metric. Coverage = dollars in connected accounts ÷ total dollars, shown next to net worth: this is the honest confidence interval on every other number on the tab, and no consumer app shows it (spine row 22 trap).</t>
+        </is>
+      </c>
+      <c r="F20" s="44" t="inlineStr">
+        <is>
+          <t>ACCOUNTS_FROM_SETUP · ACCOUNT_NAMES · ACCOUNT_SHARE_OF_TOTAL · ACCOUNT_SPLIT · ACCOUNT_TYPE_FACTS · ALLOCATION_BY_CLASS (+26 more)</t>
+        </is>
+      </c>
+      <c r="G20" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 32 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="54" t="inlineStr">
+        <is>
+          <t>SECTION B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B22" s="44" t="inlineStr">
+        <is>
+          <t>Period return</t>
+        </is>
+      </c>
+      <c r="C22" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D22" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E22" s="44" t="inlineStr">
+        <is>
+          <t>Refuse the rate. Never back-solve the beginning value from today minus the ledger — on the founder's own Vanguard account that produced minus $448,028 against a statement's $378,022 (snapshots.ts:1-13). Show the dollars instead: "worth $X today; $Y went in and $Z came out since &lt;first recorded date&gt;" (master 9 B16). The person can supply it: type a statement value with its date, kept as "as you entered it". A flow with no date: fall back from Modified Dietz to Simple Dietz — assume mid-period, and say so on screen; it is a stated assumption, not a hidden one (master 1 K16; audit 5).</t>
+        </is>
+      </c>
+      <c r="F22" s="44" t="inlineStr">
+        <is>
+          <t>VALUE_WEIGHTED_RETURN</t>
+        </is>
+      </c>
+      <c r="G22" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 1 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B23" s="44" t="inlineStr">
+        <is>
+          <t>Dollar gain</t>
+        </is>
+      </c>
+      <c r="C23" s="44" t="n">
+        <v>12</v>
+      </c>
+      <c r="D23" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="44" t="inlineStr">
+        <is>
+          <t>Gain = end − beginning − net flows; with no beginning value there is no gain figure, full stop. Show what we do have: worth today, money in, money out, income received — each "since &lt;first recorded date&gt;". Do not show a gain "since install" dressed as a longer period (master 9 B20). Person supplies: a statement value with its date.</t>
+        </is>
+      </c>
+      <c r="F23" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="48" t="inlineStr">
+        <is>
+          <t>NOT YET MAPPED</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B24" s="44" t="inlineStr">
+        <is>
+          <t>Return by holding</t>
+        </is>
+      </c>
+      <c r="C24" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D24" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="44" t="inlineStr">
+        <is>
+          <t>Basis missing → NO percentage and NO gain figure. Show value, units, income received, and: "We don't know what you paid for this. Add what you paid — or the purchase date and we'll look up the price." Never treat missing basis as zero: that reports the entire value as gain (the engine already skips such lots rather than calling shares free — master 2 r62). Quantity missing → we cannot even value it ourselves; if the broker states a market value, show it tagged "as stated by your broker", with no per-share figures and no return, and ask for the share count.</t>
+        </is>
+      </c>
+      <c r="F24" s="44" t="inlineStr">
+        <is>
+          <t>HOLDING_TOTAL_ROI · LOOK_BACK</t>
+        </is>
+      </c>
+      <c r="G24" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 2 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B25" s="44" t="inlineStr">
+        <is>
+          <t>Contribution to return</t>
+        </is>
+      </c>
+      <c r="C25" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D25" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="44" t="inlineStr">
+        <is>
+          <t>Attribution needs BEGINNING weights: weight at period start × that holding's period return (master 1 K30). No start snapshot → no attribution; show since-purchase gain per holding, ranked, labelled "since you bought them — not what drove this period".</t>
+        </is>
+      </c>
+      <c r="F25" s="44" t="inlineStr">
+        <is>
+          <t>WHAT_DROVE_THE_RETURN</t>
+        </is>
+      </c>
+      <c r="G25" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 1 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B26" s="44" t="inlineStr">
+        <is>
+          <t>Benchmark comparison</t>
+        </is>
+      </c>
+      <c r="C26" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D26" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="44" t="inlineStr">
+        <is>
+          <t>The difference is time-weighted portfolio return minus index return over identical dates — nothing else may be subtracted. Until the daily series exists, show the two numbers side by side — our money-weighted figure and the index's own — and print NO difference: "these answer different questions" (master 1 K32; audit 15). Today the live engine blends benchmarks against a money-weighted number and prints "beat by" (master 2 r70) — that line comes down.</t>
+        </is>
+      </c>
+      <c r="F26" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="48" t="inlineStr">
+        <is>
+          <t>NOT YET MAPPED</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B27" s="44" t="inlineStr">
+        <is>
+          <t>Income earned</t>
+        </is>
+      </c>
+      <c r="C27" s="44" t="n">
+        <v>24</v>
+      </c>
+      <c r="D27" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="44" t="inlineStr">
+        <is>
+          <t>Income there is UNKNOWN, not zero: "we can't see income for accounts without transaction history" — a manual account's interest is invisible and the total must say the household figure excludes it. Person supplies: connect the account or add income entries.</t>
+        </is>
+      </c>
+      <c r="F27" s="44" t="inlineStr">
+        <is>
+          <t>LOOK_BACK</t>
+        </is>
+      </c>
+      <c r="G27" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 1 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B28" s="44" t="inlineStr">
+        <is>
+          <t>Forward income</t>
+        </is>
+      </c>
+      <c r="C28" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D28" s="49" t="inlineStr">
+        <is>
+          <t>DEFER</t>
+        </is>
+      </c>
+      <c r="E28" s="44" t="inlineStr">
+        <is>
+          <t>The formula — Σ units × annual rate per unit (dividend rate; coupon × face) — has no data source today (spine R30; master 1 K56, verified against FDX 6.3/6.4). Two honest paths: (a) show trailing-12-months received, labelled "if the last year repeats" — with the warning that a special dividend or a called bond will not; (b) buy a security-master feed (open question 3/4). A bond's coupon comes from the description text, permanently (master 1 K26); a parse failure is UNKNOWN, never zero — a 0% coupon reads as a fact and every figure built on it is confidently wrong (master 2 r37; audit 24).</t>
+        </is>
+      </c>
+      <c r="F28" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="48" t="inlineStr">
+        <is>
+          <t>NOT YET MAPPED</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B29" s="44" t="inlineStr">
+        <is>
+          <t>Yield</t>
+        </is>
+      </c>
+      <c r="C29" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D29" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E29" s="44" t="inlineStr">
+        <is>
+          <t>Annual income ÷ current value. Coupon parse failure → UNKNOWN, no yield shown, never 0% (audit 24). No value → no yield, never a division by zero (master 2 r97). Person supplies: the coupon from their statement, one field.</t>
+        </is>
+      </c>
+      <c r="F29" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="48" t="inlineStr">
+        <is>
+          <t>NOT YET MAPPED</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B30" s="44" t="inlineStr">
+        <is>
+          <t>Realised gains this tax year</t>
+        </is>
+      </c>
+      <c r="C30" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D30" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="44" t="inlineStr">
+        <is>
+          <t>Σ (proceeds − basis of the lots sold − fees) for sales in the tax year, TAXABLE accounts only. Tax type unknown → show NOTHING for that account, not an estimate — a guess invents a tax bill where the true answer may be zero (master 1 K47; audit 22); the person marks the account type once. Sold-lot basis missing → that sale shows proceeds and "gain unknown — add what you paid".</t>
+        </is>
+      </c>
+      <c r="F30" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="48" t="inlineStr">
+        <is>
+          <t>NOT YET MAPPED</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B31" s="44" t="inlineStr">
+        <is>
+          <t>Tax-loss harvesting opportunity</t>
+        </is>
+      </c>
+      <c r="C31" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D31" s="48" t="inlineStr">
+        <is>
+          <t>CUT</t>
+        </is>
+      </c>
+      <c r="E31" s="44" t="inlineStr">
+        <is>
+          <t>Lots where value &lt; basis, TAXABLE accounts only. Tax type unknown → the insight does not fire (audit 22). No real lots → we can only say the POSITION is underwater as a whole; lot-picking advice is unavailable and says so (master 8 F7; audit 51).</t>
+        </is>
+      </c>
+      <c r="F31" s="44" t="inlineStr">
+        <is>
+          <t>removed 2026-08-20</t>
+        </is>
+      </c>
+      <c r="G31" s="46" t="inlineStr">
+        <is>
+          <t>CUT — removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B32" s="44" t="inlineStr">
+        <is>
+          <t>Fees paid</t>
+        </is>
+      </c>
+      <c r="C32" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D32" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="44" t="inlineStr">
+        <is>
+          <t>Σ fee transactions in the window. No transactions → unknown, not $0 — same rule as Income earned P1-A.</t>
+        </is>
+      </c>
+      <c r="F32" s="44" t="inlineStr">
+        <is>
+          <t>LOOK_BACK</t>
+        </is>
+      </c>
+      <c r="G32" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 1 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B33" s="44" t="inlineStr">
+        <is>
+          <t>Allocation vs target, and drift</t>
+        </is>
+      </c>
+      <c r="C33" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D33" s="48" t="inlineStr">
+        <is>
+          <t>CUT</t>
+        </is>
+      </c>
+      <c r="E33" s="44" t="inlineStr">
+        <is>
+          <t>Without a target there is NO drift — only allocation. The word "drift" does not appear until a target does (master 1 K31; audit 14 — carried nowhere today). Ask for the target as a broad shape — roughly this much in shares, bonds, cash — never to the decimal, which invites nagging over a 0.4% gap that costs real money to act on.</t>
+        </is>
+      </c>
+      <c r="F33" s="44" t="inlineStr">
+        <is>
+          <t>removed 2026-08-20</t>
+        </is>
+      </c>
+      <c r="G33" s="46" t="inlineStr">
+        <is>
+          <t>CUT — removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B34" s="44" t="inlineStr">
+        <is>
+          <t>Risk measures</t>
+        </is>
+      </c>
+      <c r="C34" s="44" t="n">
+        <v>24</v>
+      </c>
+      <c r="D34" s="48" t="inlineStr">
+        <is>
+          <t>CUT</t>
+        </is>
+      </c>
+      <c r="E34" s="44" t="inlineStr">
+        <is>
+          <t>Standard deviation of periodic returns, annualised — needs the daily store, which starts the day it starts (snapshots.ts:10-12). Under ~12 months → refuse the statistic; context may show the person's INDEX's history, clearly labelled "the index's ride, not yet yours". The store also still lacks fields its own spec commits to (master 9 B8/B9 vs snapshots.ts; audit 49) — the series this metric needs must be built to that spec, not the current shape.</t>
+        </is>
+      </c>
+      <c r="F34" s="44" t="inlineStr">
+        <is>
+          <t>removed 2026-08-20</t>
+        </is>
+      </c>
+      <c r="G34" s="46" t="inlineStr">
+        <is>
+          <t>CUT — removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B35" s="44" t="inlineStr">
+        <is>
+          <t>Sequence-of-returns exposure</t>
+        </is>
+      </c>
+      <c r="C35" s="44" t="n">
+        <v>12</v>
+      </c>
+      <c r="D35" s="48" t="inlineStr">
+        <is>
+          <t>CUT</t>
+        </is>
+      </c>
+      <c r="E35" s="44" t="inlineStr">
+        <is>
+          <t>Run the SAME average return good-years-first and bad-years-first with the person's actual planned withdrawals — same average, very different endings (spine R37). Without a withdrawal plan the metric does not exist: ask for planned monthly withdrawal; meanwhile an ILLUSTRATION with round numbers, labelled "an example, not your plan", is the most the screen may show.</t>
+        </is>
+      </c>
+      <c r="F35" s="44" t="inlineStr">
+        <is>
+          <t>removed 2026-08-20</t>
+        </is>
+      </c>
+      <c r="G35" s="46" t="inlineStr">
+        <is>
+          <t>CUT — removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B36" s="44" t="inlineStr">
+        <is>
+          <t>Cash drag</t>
+        </is>
+      </c>
+      <c r="C36" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D36" s="48" t="inlineStr">
+        <is>
+          <t>CUT</t>
+        </is>
+      </c>
+      <c r="E36" s="44" t="inlineStr">
+        <is>
+          <t>Idle share = uninvested cash ÷ investable assets — and it is computable only once ONE rule for cash exists. Today three rules give three answers for the same dollars: the class rule calls a money-market fund an investment, the screen groups it under Cash, and the account screen subtracts it from cash and drops it from holdings (master 1 K37 — a live contradiction; audit 46 lists TOTAL_CASH with opposite statuses). The rule: a money-market fund is a HOLDING that pays income; Cash means the broker's uninvested balance only. Until every screen reads that one rule, this metric must not ship (open question 10).</t>
+        </is>
+      </c>
+      <c r="F36" s="44" t="inlineStr">
+        <is>
+          <t>grid: section-B.md whole section · code: idle-cash insight rule, Idle cash screen and route, their tests</t>
+        </is>
+      </c>
+      <c r="G36" s="46" t="inlineStr">
+        <is>
+          <t>CUT — removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B37" s="44" t="inlineStr">
+        <is>
+          <t>Look-through exposure</t>
+        </is>
+      </c>
+      <c r="C37" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D37" s="48" t="inlineStr">
+        <is>
+          <t>CUT</t>
+        </is>
+      </c>
+      <c r="E37" s="44" t="inlineStr">
+        <is>
+          <t>Σ (fund weight in portfolio × holding weight inside the fund) — and the inside-the-fund data must be bought or built (spine R39). Without it the screen does not exist; the honest line: "we can see your funds, not inside them yet." Never approximate from the fund's NAME — "Total Market" is a name, not a composition (open question 3).</t>
+        </is>
+      </c>
+      <c r="F37" s="44" t="inlineStr">
+        <is>
+          <t>grid: section-B.md whole section AND the look-through purpose inside Allocation by asset class (section-A.md) · code: never implemented</t>
+        </is>
+      </c>
+      <c r="G37" s="46" t="inlineStr">
+        <is>
+          <t>CUT — removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B38" s="44" t="inlineStr">
+        <is>
+          <t>Currency effect on return</t>
+        </is>
+      </c>
+      <c r="C38" s="44" t="n">
+        <v>6</v>
+      </c>
+      <c r="D38" s="49" t="inlineStr">
+        <is>
+          <t>DEFER</t>
+        </is>
+      </c>
+      <c r="E38" s="44" t="inlineStr">
+        <is>
+          <t>Three stated components: the asset's own-currency return, the currency move, and the interaction term — never one blended number (spine R40). No FX series → show the blended return labelled "includes any currency move" — never an invented split. Holding currency unknown → assume the account's, flagged; FDX allows a holding-level currency different from its account, and ignoring it sums yen and dollars (spine R21 trap).</t>
+        </is>
+      </c>
+      <c r="F38" s="44" t="inlineStr">
+        <is>
+          <t>CURRENCY</t>
+        </is>
+      </c>
+      <c r="G38" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 1 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="44" t="inlineStr">
+        <is>
+          <t>Time in market</t>
+        </is>
+      </c>
+      <c r="C39" s="44" t="n">
+        <v>12</v>
+      </c>
+      <c r="D39" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="44" t="inlineStr">
+        <is>
+          <t>Today − purchase date, per lot. With no lots, a synthetic single lot carries ONE date and every holding-period claim rests on it (spine R41 trap; audit 51) — instead show "held since at least &lt;first seen date&gt;", the earliest evidence we hold (first transaction or first snapshot), which is honest and useful. Person supplies: the purchase date, one field per holding.</t>
+        </is>
+      </c>
+      <c r="F39" s="44" t="inlineStr">
+        <is>
+          <t>ALLOCATION_BY_HOLDING_KIND · BENCHMARK_RETURN_BLENDED</t>
+        </is>
+      </c>
+      <c r="G39" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 2 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="54" t="inlineStr">
+        <is>
+          <t>SECTION C</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B41" s="44" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C41" s="44" t="n">
+        <v>24</v>
+      </c>
+      <c r="D41" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E41" s="44" t="inlineStr">
+        <is>
+          <t>Gross is worked back through the tax schedule (src/domain/income/tax.ts:47), but that function uses the SINGLE-filer schedule for everyone — a married couple's gross comes out too high (take-home $90,000 → gross overstated by $6,746). Until the filing status is passed through (Engines row 134, DEFECT), show gross for single filers only; for married filers say "We can show what lands in your account; to show before-tax pay we need your filing status" and take it in one tap. Never print the single-filer figure for a married person.</t>
+        </is>
+      </c>
+      <c r="F41" s="44" t="inlineStr">
+        <is>
+          <t>EFFECTIVE_TAX_RATE · EMPLOYER_MATCH · EQUITY_ROW_VALUE · EQUITY_THIS_YEAR · FILING_STATUS · GROSS_FROM_TAKE_HOME (+21 more)</t>
+        </is>
+      </c>
+      <c r="G41" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 27 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B42" s="44" t="inlineStr">
+        <is>
+          <t>Total spending</t>
+        </is>
+      </c>
+      <c r="C42" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D42" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E42" s="44" t="inlineStr">
+        <is>
+          <t>Show "$0 logged so far this month" as a fact about the RECORDS, never as "you spent nothing" — with the planned figure beside it clearly labelled Planned. Offer the two capture doors (receipt photo, quick add).</t>
+        </is>
+      </c>
+      <c r="F42" s="44" t="inlineStr">
+        <is>
+          <t>PLANNED_SPENDING · SPENDING_BY_KIND</t>
+        </is>
+      </c>
+      <c r="G42" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 2 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B43" s="44" t="inlineStr">
+        <is>
+          <t>Spending by category</t>
+        </is>
+      </c>
+      <c r="C43" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D43" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" s="44" t="inlineStr">
+        <is>
+          <t>A visible "Not yet sorted — $X" row of its own, never spread across the others (the same rule as the unclassified bucket on the balance sheet: an 'other' bucket that quietly holds 4% passes every test). One tap sorts them.</t>
+        </is>
+      </c>
+      <c r="F43" s="44" t="inlineStr">
+        <is>
+          <t>PLANNED_SPENDING · READ_A_RECEIPT · SPENDING_BY_KIND</t>
+        </is>
+      </c>
+      <c r="G43" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 3 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B44" s="44" t="inlineStr">
+        <is>
+          <t>Fixed vs variable vs discretionary</t>
+        </is>
+      </c>
+      <c r="C44" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D44" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" s="44" t="inlineStr">
+        <is>
+          <t>The floor cannot be separated: fall back to the WHOLE planned spend as the floor (src/domain/budget/index.ts:164, the B-33 fix) — cautious for every figure built on it — and say "we're treating all your spending as must-pay until you sort it".</t>
+        </is>
+      </c>
+      <c r="F44" s="44" t="inlineStr">
+        <is>
+          <t>DEBTS_FROM_SETUP · DEBT_ACTUAL_TOTAL · DEBT_MINIMUM_TOTAL · DEBT_PAYMENTS_ACTUAL · DEBT_PICTURE · DEBT_REQUIRED_PAYMENT (+6 more)</t>
+        </is>
+      </c>
+      <c r="G44" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 12 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B45" s="44" t="inlineStr">
+        <is>
+          <t>Recurring subscriptions</t>
+        </is>
+      </c>
+      <c r="C45" s="44" t="n">
+        <v>24</v>
+      </c>
+      <c r="D45" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="44" t="inlineStr">
+        <is>
+          <t>The honest screen is the DECLARED list: "Your repeating bills, as you've told us" (src/screens/ExpenseScreen.tsx auto-logs them on their due dates). Detection — same merchant, similar amount, regular interval — becomes possible only when a bank/card feed connects; say that plainly rather than showing an empty "we found nothing".</t>
+        </is>
+      </c>
+      <c r="F45" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="48" t="inlineStr">
+        <is>
+          <t>NOT YET MAPPED</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B46" s="44" t="inlineStr">
+        <is>
+          <t>Net cash flow</t>
+        </is>
+      </c>
+      <c r="C46" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D46" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E46" s="44" t="inlineStr">
+        <is>
+          <t>Show the PLANNED surplus (income − spending from the plan, src/domain/budget/index.ts:30) labelled Planned, and "log income and spending to see the actual". Never present the plan as the month's result.</t>
+        </is>
+      </c>
+      <c r="F46" s="44" t="inlineStr">
+        <is>
+          <t>ACCOUNTS_FROM_SETUP · ACCOUNT_NAMES · ACCOUNT_SHARE_OF_TOTAL · ACCOUNT_SPLIT · ACCOUNT_TYPE_FACTS · ALLOCATION_BY_CLASS (+27 more)</t>
+        </is>
+      </c>
+      <c r="G46" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 33 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B47" s="44" t="inlineStr">
+        <is>
+          <t>Savings rate</t>
+        </is>
+      </c>
+      <c r="C47" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D47" s="48" t="inlineStr">
+        <is>
+          <t>CUT</t>
+        </is>
+      </c>
+      <c r="E47" s="44" t="inlineStr">
+        <is>
+          <t>For a married filer, gross via the current work-back is overstated (see Income P1-A), which UNDERSTATES the gross-basis rate. Until fixed: show the take-home-basis rate instead (which needs no gross), and label the gross-basis rate "needs your filing status".</t>
+        </is>
+      </c>
+      <c r="F47" s="44" t="inlineStr">
+        <is>
+          <t>grid: section-C.md whole section · code: the two rate functions in src/domain/savings (monthlySavings stays — three screens use it); the onboarding recap line that quoted a rate</t>
+        </is>
+      </c>
+      <c r="G47" s="46" t="inlineStr">
+        <is>
+          <t>CUT — removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B48" s="44" t="inlineStr">
+        <is>
+          <t>Runway / emergency reserve</t>
+        </is>
+      </c>
+      <c r="C48" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D48" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E48" s="44" t="inlineStr">
+        <is>
+          <t>Refuse the months figure — "add your checking and savings balances to see how long you could last." A runway from $0 recorded cash reads as zero months and terrifies for no reason.</t>
+        </is>
+      </c>
+      <c r="F48" s="44" t="inlineStr">
+        <is>
+          <t>ACCOUNTS_FROM_SETUP · ACCOUNT_NAMES · ACCOUNT_SHARE_OF_TOTAL · ACCOUNT_SPLIT · ACCOUNT_TYPE_FACTS · ALLOCATION_BY_CLASS (+27 more)</t>
+        </is>
+      </c>
+      <c r="G48" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 33 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B49" s="44" t="inlineStr">
+        <is>
+          <t>Budget vs actual</t>
+        </is>
+      </c>
+      <c r="C49" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D49" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E49" s="44" t="inlineStr">
+        <is>
+          <t>Nothing to compare — show actuals and the door to set a plan. Never compare against $0 and report 100% overspend.</t>
+        </is>
+      </c>
+      <c r="F49" s="44" t="inlineStr">
+        <is>
+          <t>PLANNED_SPENDING · SPENDING_BY_KIND</t>
+        </is>
+      </c>
+      <c r="G49" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 2 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B50" s="44" t="inlineStr">
+        <is>
+          <t>Safe to spend</t>
+        </is>
+      </c>
+      <c r="C50" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D50" s="48" t="inlineStr">
+        <is>
+          <t>CUT</t>
+        </is>
+      </c>
+      <c r="E50" s="44" t="inlineStr">
+        <is>
+          <t>REFUSE the number. This metric reads as permission, and a missed bill makes it confidently wrong in the most expensive direction (spine row 52 trap). Screen: "To show what's safe to spend we need your regular bills — add them or connect the account they're paid from."</t>
+        </is>
+      </c>
+      <c r="F50" s="44" t="inlineStr">
+        <is>
+          <t>grid: section-C.md whole section · code: never implemented as a budget metric. The retiree paycheck draw ("Left to spend") is a DIFFERENT concept — withdrawal sizing, a kept core feature — and is untouched</t>
+        </is>
+      </c>
+      <c r="G50" s="46" t="inlineStr">
+        <is>
+          <t>CUT — removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B51" s="44" t="inlineStr">
+        <is>
+          <t>Cash flow forecast</t>
+        </is>
+      </c>
+      <c r="C51" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D51" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E51" s="44" t="inlineStr">
+        <is>
+          <t>Refuse — a forecast from an unknown start is a shape with no anchor. The dated-bill planner takes startBalance explicitly (src/domain/cashflow/index.ts:65); with none, ask for the checking balance, one box.</t>
+        </is>
+      </c>
+      <c r="F51" s="44" t="inlineStr">
+        <is>
+          <t>PLANNED_SPENDING · POT_AT_RETIREMENT · RETIREMENT_SPENDING · SPENDING_BY_KIND · WILL_IT_LAST</t>
+        </is>
+      </c>
+      <c r="G51" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 5 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B52" s="44" t="inlineStr">
+        <is>
+          <t>Age of money</t>
+        </is>
+      </c>
+      <c r="C52" s="44" t="n">
+        <v>6</v>
+      </c>
+      <c r="D52" s="48" t="inlineStr">
+        <is>
+          <t>CUT</t>
+        </is>
+      </c>
+      <c r="E52" s="44" t="inlineStr">
+        <is>
+          <t>Refuse the metric. The same worry — "am I living on last month's money?" — is answered honestly today by the essentials runway (Runway P2), which needs only balances. Offer that instead of a fake age.</t>
+        </is>
+      </c>
+      <c r="F52" s="44" t="inlineStr">
+        <is>
+          <t>grid: section-C.md whole section · code: never implemented</t>
+        </is>
+      </c>
+      <c r="G52" s="46" t="inlineStr">
+        <is>
+          <t>CUT — removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B53" s="44" t="inlineStr">
+        <is>
+          <t>Interest and fees paid</t>
+        </is>
+      </c>
+      <c r="C53" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D53" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E53" s="44" t="inlineStr">
+        <is>
+          <t>No interest figure for that debt — show "rate needed" on its row rather than a total that silently skips it. Every debt in the app is typed by hand (Engines row 43 works from the name the person typed; no connected road carries debts today), so the ask is one field on a debt the person already entered.</t>
+        </is>
+      </c>
+      <c r="F53" s="44" t="inlineStr">
+        <is>
+          <t>DEBTS_FROM_SETUP · DEBT_ACTUAL_TOTAL · DEBT_MINIMUM_TOTAL · DEBT_PAYMENTS_ACTUAL · DEBT_PICTURE · DEBT_REQUIRED_PAYMENT (+4 more)</t>
+        </is>
+      </c>
+      <c r="G53" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 10 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B54" s="44" t="inlineStr">
+        <is>
+          <t>Effective tax rate</t>
+        </is>
+      </c>
+      <c r="C54" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D54" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E54" s="44" t="inlineStr">
+        <is>
+          <t>Single is assumed — the cautious side for tax owed (src/domain/income/onboarding.ts:333) — and the screen says "assuming single". No state rate entered → federal-only, labelled "before state tax", never a guessed state table (stateRateOf, src/domain/income/onboarding.ts:337; the rationale at src/domain/income/tax.ts:92: one honest user-entered percent beats fifty guessed tables).</t>
+        </is>
+      </c>
+      <c r="F54" s="44" t="inlineStr">
+        <is>
+          <t>EFFECTIVE_TAX_RATE · EMPLOYER_MATCH · EQUITY_ROW_VALUE · EQUITY_THIS_YEAR · FILING_STATUS · GROSS_FROM_TAKE_HOME (+19 more)</t>
+        </is>
+      </c>
+      <c r="G54" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 25 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B55" s="44" t="inlineStr">
+        <is>
+          <t>Personal inflation</t>
+        </is>
+      </c>
+      <c r="C55" s="44" t="n">
+        <v>12</v>
+      </c>
+      <c r="D55" s="48" t="inlineStr">
+        <is>
+          <t>CUT</t>
+        </is>
+      </c>
+      <c r="E55" s="44" t="inlineStr">
+        <is>
+          <t>Refuse the personal figure. Show the published rate instead, clearly labelled as the national figure, with its fallback flag if the feed was down (src/services/economicData.ts:47 marks a stated fallback). "After two years of records we can show YOUR inflation, not the country's."</t>
+        </is>
+      </c>
+      <c r="F55" s="44" t="inlineStr">
+        <is>
+          <t>grid: section-C.md whole section · code: never implemented — inflation was always the plan assumption only</t>
+        </is>
+      </c>
+      <c r="G55" s="46" t="inlineStr">
+        <is>
+          <t>CUT — removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B56" s="44" t="inlineStr">
+        <is>
+          <t>Income replacement rate</t>
+        </is>
+      </c>
+      <c r="C56" s="44" t="n">
+        <v>6</v>
+      </c>
+      <c r="D56" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E56" s="44" t="inlineStr">
+        <is>
+          <t>The denominator cannot be measured. Ask for it: one box — "about what did you spend (or earn) per month before you retired?" — and label the resulting rate "against the figure you gave us". Refuse only if the person declines; a stated denominator honestly labelled beats no answer.</t>
+        </is>
+      </c>
+      <c r="F56" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="48" t="inlineStr">
+        <is>
+          <t>NOT YET MAPPED</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="54" t="inlineStr">
+        <is>
+          <t>SECTION D</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B58" s="44" t="inlineStr">
+        <is>
+          <t>Retirement pot</t>
+        </is>
+      </c>
+      <c r="C58" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D58" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E58" s="44" t="inlineStr">
+        <is>
+          <t>Leave it out of the pot and say so by name: "Vanguard IRA not counted — no value yet." Never a silent zero, which shrinks the pot and reads as a loss (K52). Fix: type a balance or connect the account. A missing earmark share is NOT missing — the stated default applies (R121: everything counts except the home you live in and the car you drive; a 529 is 0%).</t>
+        </is>
+      </c>
+      <c r="F58" s="44" t="inlineStr">
+        <is>
+          <t>SPLIT_BY_HOW_IT_IS_TAXED · WILL_IT_LAST · WILL_IT_LAST_RESULT</t>
+        </is>
+      </c>
+      <c r="G58" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 3 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B59" s="44" t="inlineStr">
+        <is>
+          <t>Target number</t>
+        </is>
+      </c>
+      <c r="C59" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D59" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E59" s="44" t="inlineStr">
+        <is>
+          <t>No target — 25 × nothing is not a number. Door: "tell us what a month costs." Never substitute a national average silently.</t>
+        </is>
+      </c>
+      <c r="F59" s="44" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST</t>
+        </is>
+      </c>
+      <c r="G59" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 1 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B60" s="44" t="inlineStr">
+        <is>
+          <t>Funded ratio</t>
+        </is>
+      </c>
+      <c r="C60" s="44" t="n">
+        <v>6</v>
+      </c>
+      <c r="D60" s="48" t="inlineStr">
+        <is>
+          <t>CUT</t>
+        </is>
+      </c>
+      <c r="E60" s="44" t="inlineStr">
+        <is>
+          <t>Not built as a metric: tab 2 carries no funded-ratio engine (checked 2026-08-19). The present-value machinery half-exists in code — capitalNeeded() discounts spending net of guaranteed income, plus a bequest, at a real return (retirement/index.ts:32-43, used at onboarding) — so the ratio would be pot ÷ that figure, with realReturn as the discount rate nobody has yet named on a screen. Until wired — and until spending and income are captured — the metric does not appear; the odds (R84) stay the one on-track figure. (Open question 10.)</t>
+        </is>
+      </c>
+      <c r="F60" s="44" t="inlineStr">
+        <is>
+          <t>grid: section-D.md whole section · code: never implemented (goal funded % and plan on-track % are different, kept concepts)</t>
+        </is>
+      </c>
+      <c r="G60" s="46" t="inlineStr">
+        <is>
+          <t>CUT — removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B61" s="44" t="inlineStr">
+        <is>
+          <t>Probability of success</t>
+        </is>
+      </c>
+      <c r="C61" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D61" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E61" s="44" t="inlineStr">
+        <is>
+          <t>No odds — and never a confident zero (R160). The door lists exactly what is missing (R157); until then the Sample sentence, the word Sample first (R80).</t>
+        </is>
+      </c>
+      <c r="F61" s="44" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST</t>
+        </is>
+      </c>
+      <c r="G61" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 1 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B62" s="44" t="inlineStr">
+        <is>
+          <t>Safe withdrawal rate</t>
+        </is>
+      </c>
+      <c r="C62" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D62" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E62" s="44" t="inlineStr">
+        <is>
+          <t>Nothing to size. Same door as Probability of success P1-A.</t>
+        </is>
+      </c>
+      <c r="F62" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="48" t="inlineStr">
+        <is>
+          <t>NOT YET MAPPED</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B63" s="44" t="inlineStr">
+        <is>
+          <t>Current withdrawal rate</t>
+        </is>
+      </c>
+      <c r="C63" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D63" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E63" s="44" t="inlineStr">
+        <is>
+          <t>The app has only ever stored one household number per day (tab 9 B6; audit item 49), and the start value must be built the same way as the end — positions plus cash plus interest built up since the last coupon (K6/K7; audit item 3). Until the per-account record covers 12 months: refuse the RATE, show the DOLLARS — "you took $31,000 out over the last 12 months" (tab 9 B15-B16). The new store's valueOn() supplies the denominator once wired to screens (engines/snapshots.ts:110; no screen reads it yet — checked 2026-08-19).</t>
+        </is>
+      </c>
+      <c r="F63" s="44" t="inlineStr">
+        <is>
+          <t>SPLIT_BY_HOW_IT_IS_TAXED</t>
+        </is>
+      </c>
+      <c r="G63" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 1 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B64" s="44" t="inlineStr">
+        <is>
+          <t>Portfolio longevity</t>
+        </is>
+      </c>
+      <c r="C64" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D64" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E64" s="44" t="inlineStr">
+        <is>
+          <t>Same door (R157). No guessed age, ever.</t>
+        </is>
+      </c>
+      <c r="F64" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G64" s="48" t="inlineStr">
+        <is>
+          <t>NOT YET MAPPED</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B65" s="44" t="inlineStr">
+        <is>
+          <t>Guaranteed income floor</t>
+        </is>
+      </c>
+      <c r="C65" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D65" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E65" s="44" t="inlineStr">
+        <is>
+          <t>"Not captured yet" — never "you have $0 guaranteed income"; those are different sentences. Only a stated "not eligible" means zero (R159). Fix: type Social Security and pension from the statements.</t>
+        </is>
+      </c>
+      <c r="F65" s="44" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST</t>
+        </is>
+      </c>
+      <c r="G65" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 1 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B66" s="44" t="inlineStr">
+        <is>
+          <t>Social Security decision</t>
+        </is>
+      </c>
+      <c r="C66" s="44" t="n">
+        <v>24</v>
+      </c>
+      <c r="D66" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E66" s="44" t="inlineStr">
+        <is>
+          <t>No table. We do not hold the earnings record and must not estimate the check from income — an invented benefit is the worst seed a claiming decision can have. Fix: ssa.gov → statement → type the age-67 monthly figure.</t>
+        </is>
+      </c>
+      <c r="F66" s="44" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST</t>
+        </is>
+      </c>
+      <c r="G66" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 1 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B67" s="44" t="inlineStr">
+        <is>
+          <t>Required minimum distributions</t>
+        </is>
+      </c>
+      <c r="C67" s="44" t="n">
+        <v>24</v>
+      </c>
+      <c r="D67" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E67" s="44" t="inlineStr">
+        <is>
+          <t>The IRS divides LAST December's balance; the app rarely holds it (per-account history starts when first kept — audit item 49). The custodian's own RMD letter or the January statement is the record; our figure from today's balance is an ESTIMATE and the schedule already says so in code (decumulation/index.ts:137-141). Screen: "estimated from today's balance — your custodian's letter has the exact figure."</t>
+        </is>
+      </c>
+      <c r="F67" s="44" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST</t>
+        </is>
+      </c>
+      <c r="G67" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 1 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B68" s="44" t="inlineStr">
+        <is>
+          <t>Roth conversion analysis</t>
+        </is>
+      </c>
+      <c r="C68" s="44" t="n">
+        <v>24</v>
+      </c>
+      <c r="D68" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E68" s="44" t="inlineStr">
+        <is>
+          <t>A bank feed sees net pay, never gross (spine row 43); the app holds the typed annual figure (R158). Without it: no room figure — show the method in words and ask for last year's return's taxable income as the seed.</t>
+        </is>
+      </c>
+      <c r="F68" s="44" t="inlineStr">
+        <is>
+          <t>LOOK_BACK</t>
+        </is>
+      </c>
+      <c r="G68" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 1 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B69" s="44" t="inlineStr">
+        <is>
+          <t>Withdrawal sequencing</t>
+        </is>
+      </c>
+      <c r="C69" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D69" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E69" s="44" t="inlineStr">
+        <is>
+          <t>No order — the order IS the tax types. Unconfirmed accounts silently land in "taxable" today (decumulation/index.ts:19), which puts them at the front of the invested draw — only cash sits ahead (DEFAULT_DRAW_ORDER, decumulation/index.ts:78). Screen: "confirm how each account is taxed and we can order them."</t>
+        </is>
+      </c>
+      <c r="F69" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="48" t="inlineStr">
+        <is>
+          <t>NOT YET MAPPED</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B70" s="44" t="inlineStr">
+        <is>
+          <t>Healthcare and care costs</t>
+        </is>
+      </c>
+      <c r="C70" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D70" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E70" s="44" t="inlineStr">
+        <is>
+          <t>No healthcare engine exists at all (checked src/domain 2026-08-19). The honest vehicle exists though: a yearly amount charged until a stated year — recurring_until (retirement/index.ts:82-97), built for loan payments; today only the mortgage flow feeds it (debt/mortgageOdds.ts:67) and no premium door exists (checked 2026-08-19). Ask: "what would you pay a month for cover until 65?" — the person's own marketplace quote is the source. (Open question 12.)</t>
+        </is>
+      </c>
+      <c r="F70" s="44" t="inlineStr">
+        <is>
+          <t>LOOK_BACK · WILL_IT_LAST</t>
+        </is>
+      </c>
+      <c r="G70" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 2 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B71" s="44" t="inlineStr">
+        <is>
+          <t>Stress tests</t>
+        </is>
+      </c>
+      <c r="C71" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="D71" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="44" t="inlineStr">
+        <is>
+          <t>Nothing to stress — a stress is a difference from the base. Same door as Probability of success P1-A.</t>
+        </is>
+      </c>
+      <c r="F71" s="44" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST</t>
+        </is>
+      </c>
+      <c r="G71" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 1 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B72" s="44" t="inlineStr">
+        <is>
+          <t>Legacy and estate</t>
+        </is>
+      </c>
+      <c r="C72" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D72" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="44" t="inlineStr">
+        <is>
+          <t>It is the same projection's last page (R78 reads "what is left at the end").</t>
+        </is>
+      </c>
+      <c r="F72" s="44" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST</t>
+        </is>
+      </c>
+      <c r="G72" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 1 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B73" s="44" t="inlineStr">
+        <is>
+          <t>Work-optional date</t>
+        </is>
+      </c>
+      <c r="C73" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D73" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E73" s="44" t="inlineStr">
+        <is>
+          <t>No date from guessed inputs, ever.</t>
+        </is>
+      </c>
+      <c r="F73" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="48" t="inlineStr">
+        <is>
+          <t>NOT YET MAPPED</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="54" t="inlineStr">
+        <is>
+          <t>SECTION E</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="44" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B75" s="44" t="inlineStr">
+        <is>
+          <t>Real vs nominal</t>
+        </is>
+      </c>
+      <c r="C75" s="44" t="n">
+        <v>12</v>
+      </c>
+      <c r="D75" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E75" s="44" t="inlineStr">
+        <is>
+          <t>Calculate anyway, at the stated fallback, and say so. The engine already fetches inflation and the 10-year yield separately with a per-figure fallback flag (master tab 2 row 4, ECONOMIC_FIGURES); the plan default is 2.5% when the store has nothing (src/domain/retirement/willItLast.ts:63). The screen line: "assuming 2.5% inflation — standard assumption, live figure unavailable." Never silently deflate at a rate the screen does not name.</t>
+        </is>
+      </c>
+      <c r="F75" s="44" t="inlineStr">
+        <is>
+          <t>ECONOMIC_FIGURES · ODDS_DISPLAY · POT_AT_RETIREMENT · RETIREMENT_SPENDING · SPLIT_BY_HOW_IT_IS_TAXED · SWING_FROM_RETURN (+3 more)</t>
+        </is>
+      </c>
+      <c r="G75" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 9 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="44" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B76" s="44" t="inlineStr">
+        <is>
+          <t>Pre-tax vs after-tax</t>
+        </is>
+      </c>
+      <c r="C76" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D76" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E76" s="44" t="inlineStr">
+        <is>
+          <t>Show the balance; estimate NO tax on it in either direction. Master K47 is the rule: when the tax type is unknown, tax must not be estimated at all — a guess here does not produce a slightly wrong figure, it produces a tax figure where the true answer may be zero. Screen: "How is this account taxed?" with the three-way answer; a confirmed answer is never overridden by a later sync (master tab 2 row 6, CONFIRM_TAX_TYPE). Addresses audit item 22's suppression half.</t>
+        </is>
+      </c>
+      <c r="F76" s="44" t="inlineStr">
+        <is>
+          <t>CONFIRM_TAX_TYPE · GROSS_FROM_TAKE_HOME · TAX_TREATMENT</t>
+        </is>
+      </c>
+      <c r="G76" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 3 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="44" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B77" s="44" t="inlineStr">
+        <is>
+          <t>Household vs individual</t>
+        </is>
+      </c>
+      <c r="C77" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D77" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E77" s="44" t="inlineStr">
+        <is>
+          <t>The household total needs no owner: every account counts once. What breaks it is an account outside the app — a spouse's unconnected 401(k). The total says what it covers ("4 connected, 2 you typed") via the gap list (master tab 2 row 44, WHAT_IS_MISSING). And a transfer TO an owned-but-absent account must not book as money leaving the household: today flows cancel only within the measured set (master tab 2 row 76, PERSONAL_FLOWS; audit item 30) — the fix is K10's rule: net across the household, hold an unmatched leg as pending, and let the person name the far account as their own.</t>
+        </is>
+      </c>
+      <c r="F77" s="44" t="inlineStr">
+        <is>
+          <t>ACCOUNTS_FROM_SETUP · ACCOUNT_NAMES · ACCOUNT_SHARE_OF_TOTAL · ACCOUNT_SPLIT · ACCOUNT_TYPE_FACTS · ALLOCATION_BY_CLASS (+27 more)</t>
+        </is>
+      </c>
+      <c r="G77" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 33 engine(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="44" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B78" s="44" t="inlineStr">
+        <is>
+          <t>Period conventions</t>
+        </is>
+      </c>
+      <c r="C78" s="44" t="n">
+        <v>6</v>
+      </c>
+      <c r="D78" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E78" s="44" t="inlineStr">
+        <is>
+          <t>A dated-flow formula (Modified Dietz) cannot place an undated flow. The documented fallback is Simple Dietz — it assumes the flow landed mid-period, a stated assumption rather than a hidden one (master K16; audit item 5 says this fallback is written nowhere downstream — it must get a row). No snapshot at the window start → the figure refuses with "no record that far back" instead of silently measuring from a nearer day (master tab 2 row 46 recommended fix).</t>
+        </is>
+      </c>
+      <c r="F78" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="48" t="inlineStr">
+        <is>
+          <t>NOT YET MAPPED</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="44" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B79" s="44" t="inlineStr">
+        <is>
+          <t>Confidence and provenance</t>
+        </is>
+      </c>
+      <c r="C79" s="44" t="n">
+        <v>6</v>
+      </c>
+      <c r="D79" s="46" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+      <c r="E79" s="44" t="inlineStr">
+        <is>
+          <t>A missing ingredient never becomes zero or a guess; the figure that needs it is ABSENT and the screen names the gap and the door. No price → "we could not price this", visibly, never a silent $0 that reads as a loss (master K52). No cost basis → no gain figure; "add what you paid" is the door. No quantity → show the institution's own stated value if it sent one, labelled as the broker's figure; no per-share arithmetic and no gain until units arrive. "Refuse" always means: show the dollars we do know, then one plain reason — "a percentage here would mislead you" — never a blank (master tab 9 B16–B17).</t>
+        </is>
+      </c>
+      <c r="F79" s="44" t="inlineStr">
+        <is>
+          <t>POT_AT_RETIREMENT · RETIREMENT_SPENDING · WILL_IT_LAST</t>
+        </is>
+      </c>
+      <c r="G79" s="46" t="inlineStr">
+        <is>
+          <t>KEPT — 3 engine(s)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A57:G57"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3585,7 +6579,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="40" t="inlineStr">
         <is>
@@ -5086,7 +8079,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00085041"/>
@@ -18505,7 +21498,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00A32D2D"/>
@@ -19654,7 +22647,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001B4D8F"/>
@@ -19735,6 +22728,14 @@
           <t>1 · Foundation  —  Depends on nothing above it.</t>
         </is>
       </c>
+      <c r="B3" s="55" t="n"/>
+      <c r="C3" s="55" t="n"/>
+      <c r="D3" s="55" t="n"/>
+      <c r="E3" s="55" t="n"/>
+      <c r="F3" s="55" t="n"/>
+      <c r="G3" s="55" t="n"/>
+      <c r="H3" s="55" t="n"/>
+      <c r="I3" s="56" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="44" t="inlineStr">
@@ -19783,6 +22784,14 @@
           <t>2 · Calculation Module  —  Pure. Depends on NOTHING — the property that lets it run outside the app.</t>
         </is>
       </c>
+      <c r="B5" s="55" t="n"/>
+      <c r="C5" s="55" t="n"/>
+      <c r="D5" s="55" t="n"/>
+      <c r="E5" s="55" t="n"/>
+      <c r="F5" s="55" t="n"/>
+      <c r="G5" s="55" t="n"/>
+      <c r="H5" s="55" t="n"/>
+      <c r="I5" s="56" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="44" t="inlineStr">
@@ -19833,6 +22842,14 @@
           <t>3 · Features  —  Each owns its own maths, and may use the foundation.</t>
         </is>
       </c>
+      <c r="B7" s="55" t="n"/>
+      <c r="C7" s="55" t="n"/>
+      <c r="D7" s="55" t="n"/>
+      <c r="E7" s="55" t="n"/>
+      <c r="F7" s="55" t="n"/>
+      <c r="G7" s="55" t="n"/>
+      <c r="H7" s="55" t="n"/>
+      <c r="I7" s="56" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="44" t="inlineStr">
@@ -20191,6 +23208,14 @@
           <t>4 · Screens &amp; shared UI  —  May use any module below. Never calculates.</t>
         </is>
       </c>
+      <c r="B17" s="55" t="n"/>
+      <c r="C17" s="55" t="n"/>
+      <c r="D17" s="55" t="n"/>
+      <c r="E17" s="55" t="n"/>
+      <c r="F17" s="55" t="n"/>
+      <c r="G17" s="55" t="n"/>
+      <c r="H17" s="55" t="n"/>
+      <c r="I17" s="56" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="44" t="inlineStr">
@@ -20241,6 +23266,14 @@
           <t>THE FOLDER MOVE — agreed 2026-08-18, not yet started</t>
         </is>
       </c>
+      <c r="B20" s="55" t="n"/>
+      <c r="C20" s="55" t="n"/>
+      <c r="D20" s="55" t="n"/>
+      <c r="E20" s="55" t="n"/>
+      <c r="F20" s="55" t="n"/>
+      <c r="G20" s="55" t="n"/>
+      <c r="H20" s="55" t="n"/>
+      <c r="I20" s="56" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="53" t="inlineStr">
@@ -20253,6 +23286,13 @@
           <t>MoneyKeel-Latest-version/ — one folder per module, holding its maths, screens, components and tests together.</t>
         </is>
       </c>
+      <c r="C21" s="55" t="n"/>
+      <c r="D21" s="55" t="n"/>
+      <c r="E21" s="55" t="n"/>
+      <c r="F21" s="55" t="n"/>
+      <c r="G21" s="55" t="n"/>
+      <c r="H21" s="55" t="n"/>
+      <c r="I21" s="56" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="53" t="inlineStr">
@@ -20265,6 +23305,13 @@
           <t>@net-worth/… rather than a trail of ../../, so a file can move within its module without touching anything else.</t>
         </is>
       </c>
+      <c r="C22" s="55" t="n"/>
+      <c r="D22" s="55" t="n"/>
+      <c r="E22" s="55" t="n"/>
+      <c r="F22" s="55" t="n"/>
+      <c r="G22" s="55" t="n"/>
+      <c r="H22" s="55" t="n"/>
+      <c r="I22" s="56" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="53" t="inlineStr">
@@ -20277,6 +23324,13 @@
           <t>The files in app/ are one-line re-exports and routing is decided by their path, so they do not move.</t>
         </is>
       </c>
+      <c r="C23" s="55" t="n"/>
+      <c r="D23" s="55" t="n"/>
+      <c r="E23" s="55" t="n"/>
+      <c r="F23" s="55" t="n"/>
+      <c r="G23" s="55" t="n"/>
+      <c r="H23" s="55" t="n"/>
+      <c r="I23" s="56" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="53" t="inlineStr">
@@ -20289,6 +23343,13 @@
           <t>older-code-&lt;date&gt;/ per RELEASE, matching the build number. Two kept; a third is deleted.</t>
         </is>
       </c>
+      <c r="C24" s="55" t="n"/>
+      <c r="D24" s="55" t="n"/>
+      <c r="E24" s="55" t="n"/>
+      <c r="F24" s="55" t="n"/>
+      <c r="G24" s="55" t="n"/>
+      <c r="H24" s="55" t="n"/>
+      <c r="I24" s="56" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="53" t="inlineStr">
@@ -20301,6 +23362,13 @@
           <t>Out of the typechecker, out of the test runner and bundler, and a guard test that fails the build if any live file imports from an older-code folder. Without all three, archived code inside the source tree gets compiled, tested, and can be IMPORTED — the stale-code problem arriving through the back door.</t>
         </is>
       </c>
+      <c r="C25" s="55" t="n"/>
+      <c r="D25" s="55" t="n"/>
+      <c r="E25" s="55" t="n"/>
+      <c r="F25" s="55" t="n"/>
+      <c r="G25" s="55" t="n"/>
+      <c r="H25" s="55" t="n"/>
+      <c r="I25" s="56" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="53" t="inlineStr">
@@ -20313,6 +23381,13 @@
           <t>One module at a time behind a green suite: debt first (4 source, 4 tests, few dependents), then the small self-contained ones, then net worth, cash flow and plan, then setup, shared UI and foundation last.</t>
         </is>
       </c>
+      <c r="C26" s="55" t="n"/>
+      <c r="D26" s="55" t="n"/>
+      <c r="E26" s="55" t="n"/>
+      <c r="F26" s="55" t="n"/>
+      <c r="G26" s="55" t="n"/>
+      <c r="H26" s="55" t="n"/>
+      <c r="I26" s="56" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="53" t="inlineStr">
@@ -20325,6 +23400,13 @@
           <t>When the last module leaves. Two places to look is the problem being solved.</t>
         </is>
       </c>
+      <c r="C27" s="55" t="n"/>
+      <c r="D27" s="55" t="n"/>
+      <c r="E27" s="55" t="n"/>
+      <c r="F27" s="55" t="n"/>
+      <c r="G27" s="55" t="n"/>
+      <c r="H27" s="55" t="n"/>
+      <c r="I27" s="56" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="53" t="inlineStr">
@@ -20337,13 +23419,20 @@
           <t>git already keeps every version forever. The archive folders earn their place by being VISIBLE without a command, but they sit on top of the real history rather than being it — which is why keeping two is safe.</t>
         </is>
       </c>
+      <c r="C28" s="55" t="n"/>
+      <c r="D28" s="55" t="n"/>
+      <c r="E28" s="55" t="n"/>
+      <c r="F28" s="55" t="n"/>
+      <c r="G28" s="55" t="n"/>
+      <c r="H28" s="55" t="n"/>
+      <c r="I28" s="56" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B25:I25"/>
     <mergeCell ref="A5:I5"/>
-    <mergeCell ref="B25:I25"/>
     <mergeCell ref="B24:I24"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A17:I17"/>
@@ -20359,7 +23448,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23639,7 +26728,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25330,7 +28419,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25846,319 +28935,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="17" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>Cost basis - three definitions, one decision table</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>Named on the Gaps tab, resolved here. The three are not interchangeable and the weakest is the one MoneyKeel currently holds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="34" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="B4" s="34" t="inlineStr">
-        <is>
-          <t>What it includes</t>
-        </is>
-      </c>
-      <c r="C4" s="34" t="inlineStr">
-        <is>
-          <t>Who gives you this</t>
-        </is>
-      </c>
-      <c r="D4" s="34" t="inlineStr">
-        <is>
-          <t>Worth for tax reporting</t>
-        </is>
-      </c>
-      <c r="E4" s="34" t="inlineStr">
-        <is>
-          <t>What it does to unrealised gain</t>
-        </is>
-      </c>
-      <c r="F4" s="34" t="inlineStr">
-        <is>
-          <t>What the screen must say when this is all you hold</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="35" t="inlineStr">
-        <is>
-          <t>THE THREE DEFINITIONS</t>
-        </is>
-      </c>
-      <c r="B5" s="35" t="n"/>
-      <c r="C5" s="35" t="n"/>
-      <c r="D5" s="35" t="n"/>
-      <c r="E5" s="35" t="n"/>
-      <c r="F5" s="35" t="n"/>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="36" t="inlineStr">
-        <is>
-          <t>Lot-level, fees included</t>
-        </is>
-      </c>
-      <c r="B6" s="36" t="inlineStr">
-        <is>
-          <t>Each batch of shares, its own purchase date and price, with commission and fees added in. Adjusted over time by reinvested income (up) and return of capital (down).</t>
-        </is>
-      </c>
-      <c r="C6" s="36" t="inlineStr">
-        <is>
-          <t>FDX taxLots[].costBasis and Plaid Core Exchange taxLots[] where the institution supports lots; SnapTrade tax_lots[] where the institution supports lots. Both of MoneyKeel's live brokers sent NONE.</t>
-        </is>
-      </c>
-      <c r="D6" s="36" t="inlineStr">
-        <is>
-          <t>The only one that can produce a defensible long-versus-short split, because only it holds a real purchase date per batch. Still an estimate: the broker's own 1099-B is what the IRS sees.</t>
-        </is>
-      </c>
-      <c r="E6" s="36" t="inlineStr">
-        <is>
-          <t>Correct, and correct per batch - which is what a person needs when deciding which shares to sell.</t>
-        </is>
-      </c>
-      <c r="F6" s="36" t="inlineStr">
-        <is>
-          <t>Nothing special. Say which lots the figures came from.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="36" t="inlineStr">
-        <is>
-          <t>Holding average, commission included</t>
-        </is>
-      </c>
-      <c r="B7" s="36" t="inlineStr">
-        <is>
-          <t>One average cost per share across the whole position, with commission in. No purchase dates.</t>
-        </is>
-      </c>
-      <c r="C7" s="36" t="inlineStr">
-        <is>
-          <t>Yodlee costBasis. SnapTrade average_purchase_price (whether fees are inside is per broker - UNKNOWN in general).</t>
-        </is>
-      </c>
-      <c r="D7" s="36" t="inlineStr">
-        <is>
-          <t>Enough for a total gain figure. CANNOT split long from short, because there is no purchase date to judge. Mutual funds are commonly held this way by the broker too, so for funds this often matches what the broker reports.</t>
-        </is>
-      </c>
-      <c r="E7" s="36" t="inlineStr">
-        <is>
-          <t>Correct in total, meaningless per batch.</t>
-        </is>
-      </c>
-      <c r="F7" s="36" t="inlineStr">
-        <is>
-          <t>'This is an average across all your shares - we cannot tell which were bought when, so we cannot split the tax treatment.' Then show no long-versus-short split at all rather than a guessed one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="36" t="inlineStr">
-        <is>
-          <t>Price x units, fees excluded</t>
-        </is>
-      </c>
-      <c r="B8" s="36" t="inlineStr">
-        <is>
-          <t>Units multiplied by a purchase price. No commission, no fees, no adjustments.</t>
-        </is>
-      </c>
-      <c r="C8" s="36" t="inlineStr">
-        <is>
-          <t>What you get when you derive basis from FDX purchasedPrice x units - FDX carries NO fee field on a holding. This is MoneyKeel's current position: one synthetic lot built from an average price.</t>
-        </is>
-      </c>
-      <c r="D8" s="36" t="inlineStr">
-        <is>
-          <t>Weakest. It understates cost, so it OVERSTATES gain and overstates the tax owed. Never present it as a tax figure.</t>
-        </is>
-      </c>
-      <c r="E8" s="36" t="inlineStr">
-        <is>
-          <t>Overstates the gain by the fees paid, and by every reinvested distribution not added back.</t>
-        </is>
-      </c>
-      <c r="F8" s="36" t="inlineStr">
-        <is>
-          <t>'Estimated from the average price we were given. It does not include trading costs, so your real gain is likely smaller than this.' This is MoneyKeel's live state today and the sentence is missing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="35" t="inlineStr">
-        <is>
-          <t>THE DECISION</t>
-        </is>
-      </c>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n"/>
-      <c r="F9" s="35" t="n"/>
-    </row>
-    <row r="10" ht="56" customHeight="1">
-      <c r="A10" s="36" t="inlineStr">
-        <is>
-          <t>Store the tag, not just the number</t>
-        </is>
-      </c>
-      <c r="B10" s="36" t="inlineStr">
-        <is>
-          <t>Every basis figure carries which of the three it is, and where it came from. Two figures with different tags are never added, compared, or shown in the same total without saying so.</t>
-        </is>
-      </c>
-      <c r="C10" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="56" customHeight="1">
-      <c r="A11" s="36" t="inlineStr">
-        <is>
-          <t>Rank, and fall back downward only</t>
-        </is>
-      </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Lot-with-fees beats holding-average beats price-x-units. Take the best available per holding, per broker - not one choice for the whole app - and never upgrade a weaker figure by inventing the missing part.</t>
-        </is>
-      </c>
-      <c r="C11" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="98" customHeight="1">
-      <c r="A12" s="36" t="inlineStr">
-        <is>
-          <t>Basis is not static</t>
-        </is>
-      </c>
-      <c r="B12" s="36" t="inlineStr">
-        <is>
-          <t>Whatever the source, the app must adjust it as events arrive: reinvested income increases it, return of capital reduces it, a split leaves the total unchanged but changes it per share, an in-kind transfer must carry it across. A basis copied once from a broker and never adjusted drifts furthest for the long-held fund positions this audience has most of.</t>
-        </is>
-      </c>
-      <c r="C12" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="84" customHeight="1">
-      <c r="A13" s="36" t="inlineStr">
-        <is>
-          <t>What the person sees</t>
-        </is>
-      </c>
-      <c r="B13" s="36" t="inlineStr">
-        <is>
-          <t>One line under every gain figure naming the weakest ingredient in it. A retiree does not need the word 'provenance'; they need to know whether the number is good enough to act on. 'Good enough to see how you're doing, not good enough for your tax return' is the honest version, and it is true for all three definitions.</t>
-        </is>
-      </c>
-      <c r="C13" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>